--- a/Geerts 2023 Figure 3.xlsx
+++ b/Geerts 2023 Figure 3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elber\Documents\git\JSON2SBML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D4BE9C6-91F2-45EA-B34A-7230C3356E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ADC0C43D-A9F3-4477-B507-3098A7F4F117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{9ED6A267-9247-42AA-8654-D33B0E6EB95C}"/>
   </bookViews>
@@ -919,13 +919,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB074D3C-20B9-4CA3-A354-3026C0277431}">
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:H509"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.61328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -942,7 +942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -958,8 +958,16 @@
       <c r="E2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G2">
+        <f>C2*24*365</f>
+        <v>175200</v>
+      </c>
+      <c r="H2">
+        <f>D2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -975,8 +983,16 @@
       <c r="E3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G3">
+        <f t="shared" ref="G3:G66" si="0">C3*24*365</f>
+        <v>180852.13902599999</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H66" si="1">D3</f>
+        <v>1.0036578869999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -992,8 +1008,16 @@
       <c r="E4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>192479.15571360002</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1009,8 +1033,16 @@
       <c r="E5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>204106.17240119999</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1026,8 +1058,16 @@
       <c r="E6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>215733.18917639999</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1043,8 +1083,16 @@
       <c r="E7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>227360.20586400002</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1060,8 +1108,16 @@
       <c r="E8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>238987.22255159999</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1077,8 +1133,16 @@
       <c r="E9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>250614.23923919999</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1094,8 +1158,16 @@
       <c r="E10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>262241.25601439999</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>1.0052540729999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1111,8 +1183,16 @@
       <c r="E11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>273868.27270199999</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1128,8 +1208,16 @@
       <c r="E12" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>285495.28938959993</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1145,8 +1233,16 @@
       <c r="E13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>297122.30616480001</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1162,8 +1258,16 @@
       <c r="E14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>308749.32285239996</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -1179,8 +1283,16 @@
       <c r="E15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>320376.33954000002</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1196,8 +1308,16 @@
       <c r="E16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>332003.35622760002</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1213,8 +1333,16 @@
       <c r="E17" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>343630.37300279998</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>1.0052540729999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1230,8 +1358,16 @@
       <c r="E18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>355257.38969040004</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1247,8 +1383,16 @@
       <c r="E19" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>366884.40637799999</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1264,8 +1408,16 @@
       <c r="E20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>378511.42306559999</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1281,8 +1433,16 @@
       <c r="E21" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>390138.43984080001</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1298,8 +1458,16 @@
       <c r="E22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>401765.45652840001</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -1315,8 +1483,16 @@
       <c r="E23" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>413392.47321600007</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1332,8 +1508,16 @@
       <c r="E24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>425019.48990360001</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1349,8 +1533,16 @@
       <c r="E25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>436646.50667879998</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>1.0056087819999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1366,8 +1558,16 @@
       <c r="E26" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>448273.52336640004</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1383,8 +1583,16 @@
       <c r="E27" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>459900.54005400004</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1400,8 +1608,16 @@
       <c r="E28" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>471527.5567416001</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1417,8 +1633,16 @@
       <c r="E29" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>483154.57351680001</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>1.004367303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1434,8 +1658,16 @@
       <c r="E30" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>494781.59020440001</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -1451,8 +1683,16 @@
       <c r="E31" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>506408.60689200001</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1468,8 +1708,16 @@
       <c r="E32" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>518035.62357960001</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>1.004899365</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1485,8 +1733,16 @@
       <c r="E33" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>529662.64035480004</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>1.005786136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1502,8 +1758,16 @@
       <c r="E34" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>541289.6570424001</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>1.004367303</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1519,8 +1783,16 @@
       <c r="E35" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>552916.67372999992</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>1.0022390539999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1536,8 +1808,16 @@
       <c r="E36" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>564543.69041759998</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>1.0083873290000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1553,8 +1833,16 @@
       <c r="E37" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>576170.70719280001</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>1.027364213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1570,8 +1858,16 @@
       <c r="E38" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>587797.72388040007</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>1.053494379</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1587,8 +1883,16 @@
       <c r="E39" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>597839.23829639994</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>1.0946405219999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1604,8 +1908,16 @@
       <c r="E40" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>605238.24895559996</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>1.1424374420000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -1621,8 +1933,16 @@
       <c r="E41" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>610523.25655679998</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>1.1868202969999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -1638,8 +1958,16 @@
       <c r="E42" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>614751.2625851999</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>1.230227704</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -1655,8 +1983,16 @@
       <c r="E43" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G43">
+        <f t="shared" si="0"/>
+        <v>618979.26870120002</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>1.2780246239999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -1672,8 +2008,16 @@
       <c r="E44" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G44">
+        <f t="shared" si="0"/>
+        <v>623207.27472960006</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>1.3297233340000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -1689,8 +2033,16 @@
       <c r="E45" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G45">
+        <f t="shared" si="0"/>
+        <v>626906.78005920001</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>1.3781705529999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1706,8 +2058,16 @@
       <c r="E46" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G46">
+        <f t="shared" si="0"/>
+        <v>630077.78460240003</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>1.4197896400000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -1723,8 +2083,16 @@
       <c r="E47" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G47">
+        <f t="shared" si="0"/>
+        <v>633248.78914560005</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>1.4620590250000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -1740,8 +2108,16 @@
       <c r="E48" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>636948.29447520012</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>1.5106688180000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -1757,8 +2133,16 @@
       <c r="E49" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G49">
+        <f t="shared" si="0"/>
+        <v>641176.30059119989</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>1.5652938700000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1774,8 +2158,16 @@
       <c r="E50" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>645404.30661960004</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>1.6165048559999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -1791,8 +2183,16 @@
       <c r="E51" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>649632.31273560005</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>1.6667403949999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1808,8 +2208,16 @@
       <c r="E52" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>653860.31876400008</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>1.7145373150000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -1825,8 +2233,16 @@
       <c r="E53" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G53">
+        <f t="shared" si="0"/>
+        <v>658088.32488000009</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>1.758432446</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -1842,8 +2258,16 @@
       <c r="E54" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G54">
+        <f t="shared" si="0"/>
+        <v>662316.33099599998</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>1.801839854</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -1859,8 +2283,16 @@
       <c r="E55" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>667072.83781080006</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>1.8476858789999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -1876,8 +2308,16 @@
       <c r="E56" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G56">
+        <f t="shared" si="0"/>
+        <v>672357.84541200008</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>1.8952877100000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -1893,8 +2333,16 @@
       <c r="E57" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G57">
+        <f t="shared" si="0"/>
+        <v>677642.8530132001</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>1.9401582879999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -1910,8 +2358,16 @@
       <c r="E58" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>682927.86061440001</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>1.9815172560000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -1927,8 +2383,16 @@
       <c r="E59" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G59">
+        <f t="shared" si="0"/>
+        <v>688741.36891439999</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>2.0252172979999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -1944,8 +2408,16 @@
       <c r="E60" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G60">
+        <f t="shared" si="0"/>
+        <v>695083.3780884</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>2.0694375780000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -1961,8 +2433,16 @@
       <c r="E61" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G61">
+        <f t="shared" si="0"/>
+        <v>701425.38717480004</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>2.1104063669999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -1978,8 +2458,16 @@
       <c r="E62" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G62">
+        <f t="shared" si="0"/>
+        <v>708295.89704760001</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>2.151468055</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -1995,8 +2483,16 @@
       <c r="E63" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G63">
+        <f t="shared" si="0"/>
+        <v>716223.4084056</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>2.1959205850000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -2012,8 +2508,16 @@
       <c r="E64" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G64">
+        <f t="shared" si="0"/>
+        <v>724679.42054999992</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>2.2390841300000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -2029,8 +2533,16 @@
       <c r="E65" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G65">
+        <f t="shared" si="0"/>
+        <v>733663.93348080001</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>2.2812180369999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -2046,8 +2558,16 @@
       <c r="E66" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G66">
+        <f t="shared" si="0"/>
+        <v>743705.44789679989</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>2.3238992779999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -2063,8 +2583,16 @@
       <c r="E67" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G67">
+        <f t="shared" ref="G67:G129" si="2">C67*24*365</f>
+        <v>754803.9638856001</v>
+      </c>
+      <c r="H67">
+        <f t="shared" ref="H67:H129" si="3">D67</f>
+        <v>2.3666238719999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -2080,8 +2608,16 @@
       <c r="E68" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G68">
+        <f t="shared" si="2"/>
+        <v>766430.98057319992</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="3"/>
+        <v>2.4070605980000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2097,8 +2633,16 @@
       <c r="E69" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G69">
+        <f t="shared" si="2"/>
+        <v>778057.99726079986</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="3"/>
+        <v>2.4432408269999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -2114,8 +2658,16 @@
       <c r="E70" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G70">
+        <f t="shared" si="2"/>
+        <v>789685.01403600001</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="3"/>
+        <v>2.4764060379999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -2131,8 +2683,16 @@
       <c r="E71" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G71">
+        <f t="shared" si="2"/>
+        <v>801312.03072360007</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="3"/>
+        <v>2.5058468120000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -2148,8 +2708,16 @@
       <c r="E72" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G72">
+        <f t="shared" si="2"/>
+        <v>812939.04741120012</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="3"/>
+        <v>2.5329819840000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -2165,8 +2733,16 @@
       <c r="E73" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G73">
+        <f t="shared" si="2"/>
+        <v>824566.06409879995</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="3"/>
+        <v>2.5579889069999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -2182,8 +2758,16 @@
       <c r="E74" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G74">
+        <f t="shared" si="2"/>
+        <v>836193.08087399998</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="3"/>
+        <v>2.5808675810000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -2199,8 +2783,16 @@
       <c r="E75" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G75">
+        <f t="shared" si="2"/>
+        <v>847820.09756160004</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="3"/>
+        <v>2.601440653</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -2216,8 +2808,16 @@
       <c r="E76" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G76">
+        <f t="shared" si="2"/>
+        <v>859447.11424920009</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="3"/>
+        <v>2.6205948920000002</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -2233,8 +2833,16 @@
       <c r="E77" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G77">
+        <f t="shared" si="2"/>
+        <v>870651.33032519999</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="3"/>
+        <v>2.637017878</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -2250,8 +2858,16 @@
       <c r="E78" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G78">
+        <f t="shared" si="2"/>
+        <v>553973.67521520006</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="3"/>
+        <v>1.01731415</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -2267,8 +2883,16 @@
       <c r="E79" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G79">
+        <f t="shared" si="2"/>
+        <v>565600.69199039997</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="3"/>
+        <v>1.0332760160000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -2284,8 +2908,16 @@
       <c r="E80" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G80">
+        <f t="shared" si="2"/>
+        <v>576699.20789159997</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="3"/>
+        <v>1.0626458489999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -2301,8 +2933,16 @@
       <c r="E81" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G81">
+        <f t="shared" si="2"/>
+        <v>585683.72082240006</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="3"/>
+        <v>1.1055097920000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -2318,8 +2958,16 @@
       <c r="E82" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G82">
+        <f t="shared" si="2"/>
+        <v>592025.72990879999</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="3"/>
+        <v>1.149655753</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -2335,8 +2983,16 @@
       <c r="E83" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G83">
+        <f t="shared" si="2"/>
+        <v>596782.23681120004</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="3"/>
+        <v>1.1912098099999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -2352,8 +3008,16 @@
       <c r="E84" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G84">
+        <f t="shared" si="2"/>
+        <v>601010.24283959996</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="3"/>
+        <v>1.236080388</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -2369,8 +3033,16 @@
       <c r="E85" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G85">
+        <f t="shared" si="2"/>
+        <v>605238.24895559996</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="3"/>
+        <v>1.286315927</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -2386,8 +3058,16 @@
       <c r="E86" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G86">
+        <f t="shared" si="2"/>
+        <v>608937.75428520003</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="3"/>
+        <v>1.3326496759999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -2403,8 +3083,16 @@
       <c r="E87" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G87">
+        <f t="shared" si="2"/>
+        <v>612108.75882839994</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="3"/>
+        <v>1.3742687629999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -2420,8 +3108,16 @@
       <c r="E88" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G88">
+        <f t="shared" si="2"/>
+        <v>615279.76337159995</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="3"/>
+        <v>1.417188447</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -2437,8 +3133,16 @@
       <c r="E89" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G89">
+        <f t="shared" si="2"/>
+        <v>618450.76791479986</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="3"/>
+        <v>1.459457832</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -2454,8 +3158,16 @@
       <c r="E90" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G90">
+        <f t="shared" si="2"/>
+        <v>621621.77245800011</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="3"/>
+        <v>1.5017272180000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -2471,8 +3183,16 @@
       <c r="E91" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G91">
+        <f t="shared" si="2"/>
+        <v>624792.77700120001</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="3"/>
+        <v>1.5439966030000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -2488,8 +3208,16 @@
       <c r="E92" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G92">
+        <f t="shared" si="2"/>
+        <v>627963.781632</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="3"/>
+        <v>1.58561569</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -2505,8 +3233,16 @@
       <c r="E93" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G93">
+        <f t="shared" si="2"/>
+        <v>631663.28687399998</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="3"/>
+        <v>1.6321120140000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -2522,8 +3258,16 @@
       <c r="E94" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G94">
+        <f t="shared" si="2"/>
+        <v>635891.29298999999</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="3"/>
+        <v>1.6823475530000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -2539,8 +3283,16 @@
       <c r="E95" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G95">
+        <f t="shared" si="2"/>
+        <v>640119.29901840002</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="3"/>
+        <v>1.730632197</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -2556,8 +3308,16 @@
       <c r="E96" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G96">
+        <f t="shared" si="2"/>
+        <v>644347.30513440003</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="3"/>
+        <v>1.776965946</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -2573,8 +3333,16 @@
       <c r="E97" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G97">
+        <f t="shared" si="2"/>
+        <v>648575.31125039991</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="3"/>
+        <v>1.8203733529999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -2590,8 +3358,16 @@
       <c r="E98" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G98">
+        <f t="shared" si="2"/>
+        <v>652803.31727879995</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="3"/>
+        <v>1.8618298659999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -2607,8 +3383,16 @@
       <c r="E99" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G99">
+        <f t="shared" si="2"/>
+        <v>657559.82409360004</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="3"/>
+        <v>1.906993078</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -2624,8 +3408,16 @@
       <c r="E100" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G100">
+        <f t="shared" si="2"/>
+        <v>662844.83169480006</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="3"/>
+        <v>1.952644015</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -2641,8 +3433,16 @@
       <c r="E101" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G101">
+        <f t="shared" si="2"/>
+        <v>668658.34008240013</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="3"/>
+        <v>1.999855666</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -2658,8 +3458,16 @@
       <c r="E102" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G102">
+        <f t="shared" si="2"/>
+        <v>675000.34916880005</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="3"/>
+        <v>2.048628034</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -2675,8 +3483,16 @@
       <c r="E103" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G103">
+        <f t="shared" si="2"/>
+        <v>681342.35834279994</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="3"/>
+        <v>2.0931734629999998</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -2692,8 +3508,16 @@
       <c r="E104" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G104">
+        <f t="shared" si="2"/>
+        <v>688212.86821560003</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="3"/>
+        <v>2.1386478900000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -2709,8 +3533,16 @@
       <c r="E105" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G105">
+        <f t="shared" si="2"/>
+        <v>695611.87878719997</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="3"/>
+        <v>2.1835184679999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -2726,8 +3558,16 @@
       <c r="E106" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G106">
+        <f t="shared" si="2"/>
+        <v>703010.88944639999</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="3"/>
+        <v>2.2242085579999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -2743,8 +3583,16 @@
       <c r="E107" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G107">
+        <f t="shared" si="2"/>
+        <v>710938.40080439998</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="3"/>
+        <v>2.2656650699999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -2760,8 +3608,16 @@
       <c r="E108" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G108">
+        <f t="shared" si="2"/>
+        <v>719922.91373519995</v>
+      </c>
+      <c r="H108">
+        <f t="shared" si="3"/>
+        <v>2.3083137960000002</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -2777,8 +3633,16 @@
       <c r="E109" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G109">
+        <f t="shared" si="2"/>
+        <v>729435.92745239998</v>
+      </c>
+      <c r="H109">
+        <f t="shared" si="3"/>
+        <v>2.349499351</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -2794,8 +3658,16 @@
       <c r="E110" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G110">
+        <f t="shared" si="2"/>
+        <v>740005.94256719993</v>
+      </c>
+      <c r="H110">
+        <f t="shared" si="3"/>
+        <v>2.3919855029999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -2811,8 +3683,16 @@
       <c r="E111" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G111">
+        <f t="shared" si="2"/>
+        <v>751632.95934239996</v>
+      </c>
+      <c r="H111">
+        <f t="shared" si="3"/>
+        <v>2.4318901670000002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -2828,8 +3708,16 @@
       <c r="E112" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G112">
+        <f t="shared" si="2"/>
+        <v>763259.97603000002</v>
+      </c>
+      <c r="H112">
+        <f t="shared" si="3"/>
+        <v>2.4693118749999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -2845,8 +3733,16 @@
       <c r="E113" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G113">
+        <f t="shared" si="2"/>
+        <v>774886.99271759996</v>
+      </c>
+      <c r="H113">
+        <f t="shared" si="3"/>
+        <v>2.5030091470000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -2862,8 +3758,16 @@
       <c r="E114" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G114">
+        <f t="shared" si="2"/>
+        <v>786514.00949279987</v>
+      </c>
+      <c r="H114">
+        <f t="shared" si="3"/>
+        <v>2.5329819840000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -2879,8 +3783,16 @@
       <c r="E115" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G115">
+        <f t="shared" si="2"/>
+        <v>798141.02618039993</v>
+      </c>
+      <c r="H115">
+        <f t="shared" si="3"/>
+        <v>2.5608265719999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -2896,8 +3808,16 @@
       <c r="E116" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G116">
+        <f t="shared" si="2"/>
+        <v>809768.04286799999</v>
+      </c>
+      <c r="H116">
+        <f t="shared" si="3"/>
+        <v>2.586010849</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -2913,8 +3833,16 @@
       <c r="E117" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G117">
+        <f t="shared" si="2"/>
+        <v>821395.05955560005</v>
+      </c>
+      <c r="H117">
+        <f t="shared" si="3"/>
+        <v>2.6090668780000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -2930,8 +3858,16 @@
       <c r="E118" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G118">
+        <f t="shared" si="2"/>
+        <v>833022.07633079984</v>
+      </c>
+      <c r="H118">
+        <f t="shared" si="3"/>
+        <v>2.629639949</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -2947,8 +3883,16 @@
       <c r="E119" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G119">
+        <f t="shared" si="2"/>
+        <v>844649.0930183999</v>
+      </c>
+      <c r="H119">
+        <f t="shared" si="3"/>
+        <v>2.648971542</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -2964,8 +3908,16 @@
       <c r="E120" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G120">
+        <f t="shared" si="2"/>
+        <v>856276.10970599996</v>
+      </c>
+      <c r="H120">
+        <f t="shared" si="3"/>
+        <v>2.6668843029999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -2981,8 +3933,16 @@
       <c r="E121" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G121">
+        <f t="shared" si="2"/>
+        <v>867903.12639360002</v>
+      </c>
+      <c r="H121">
+        <f t="shared" si="3"/>
+        <v>2.6830235230000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -2998,8 +3958,16 @@
       <c r="E122" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G122">
+        <f t="shared" si="2"/>
+        <v>874245.13556760014</v>
+      </c>
+      <c r="H122">
+        <f t="shared" si="3"/>
+        <v>2.6885214990000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -3015,8 +3983,16 @@
       <c r="E123" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G123">
+        <f t="shared" si="2"/>
+        <v>175959.53755200002</v>
+      </c>
+      <c r="H123">
+        <f t="shared" si="3"/>
+        <v>1.0037383179999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -3032,8 +4008,16 @@
       <c r="E124" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G124">
+        <f t="shared" si="2"/>
+        <v>298245.08666520001</v>
+      </c>
+      <c r="H124">
+        <f t="shared" si="3"/>
+        <v>1.0037383179999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -3049,8 +4033,16 @@
       <c r="E125" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G125">
+        <f t="shared" si="2"/>
+        <v>420530.63586599997</v>
+      </c>
+      <c r="H125">
+        <f t="shared" si="3"/>
+        <v>1.0037383179999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -3066,8 +4058,16 @@
       <c r="E126" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G126">
+        <f t="shared" si="2"/>
+        <v>507371.09822639998</v>
+      </c>
+      <c r="H126">
+        <f t="shared" si="3"/>
+        <v>1.0037383179999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -3083,8 +4083,16 @@
       <c r="E127" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G127">
+        <f t="shared" si="2"/>
+        <v>546360.69367199996</v>
+      </c>
+      <c r="H127">
+        <f t="shared" si="3"/>
+        <v>1.0102803739999999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -3100,8 +4108,16 @@
       <c r="E128" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G128">
+        <f t="shared" si="2"/>
+        <v>532182.6589883999</v>
+      </c>
+      <c r="H128">
+        <f t="shared" si="3"/>
+        <v>1.0037383179999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>9</v>
       </c>
@@ -3117,8 +4133,16 @@
       <c r="E129" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G129">
+        <f t="shared" si="2"/>
+        <v>174600.00000600002</v>
+      </c>
+      <c r="H129">
+        <f t="shared" si="3"/>
+        <v>0.135023697</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>9</v>
       </c>
@@ -3134,8 +4158,16 @@
       <c r="E130" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G130">
+        <f t="shared" ref="G130:G193" si="4">C130*24*365</f>
+        <v>182685.4095756</v>
+      </c>
+      <c r="H130">
+        <f t="shared" ref="H130:H193" si="5">D130</f>
+        <v>0.13497048</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>9</v>
       </c>
@@ -3151,8 +4183,16 @@
       <c r="E131" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G131">
+        <f t="shared" si="4"/>
+        <v>203645.18528519996</v>
+      </c>
+      <c r="H131">
+        <f t="shared" si="5"/>
+        <v>0.135512249</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>9</v>
       </c>
@@ -3168,8 +4208,16 @@
       <c r="E132" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G132">
+        <f t="shared" si="4"/>
+        <v>211850.17060680001</v>
+      </c>
+      <c r="H132">
+        <f t="shared" si="5"/>
+        <v>0.135572314</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>9</v>
       </c>
@@ -3185,8 +4233,16 @@
       <c r="E133" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G133">
+        <f t="shared" si="4"/>
+        <v>230207.8668936</v>
+      </c>
+      <c r="H133">
+        <f t="shared" si="5"/>
+        <v>0.13615106399999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>9</v>
       </c>
@@ -3202,8 +4258,16 @@
       <c r="E134" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G134">
+        <f t="shared" si="4"/>
+        <v>241158.07170240002</v>
+      </c>
+      <c r="H134">
+        <f t="shared" si="5"/>
+        <v>0.1363885</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>9</v>
       </c>
@@ -3219,8 +4283,16 @@
       <c r="E135" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G135">
+        <f t="shared" si="4"/>
+        <v>256760.32426799997</v>
+      </c>
+      <c r="H135">
+        <f t="shared" si="5"/>
+        <v>0.136718272</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -3236,8 +4308,16 @@
       <c r="E136" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G136">
+        <f t="shared" si="4"/>
+        <v>266217.78399239999</v>
+      </c>
+      <c r="H136">
+        <f t="shared" si="5"/>
+        <v>0.136925558</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>9</v>
       </c>
@@ -3253,8 +4333,16 @@
       <c r="E137" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G137">
+        <f t="shared" si="4"/>
+        <v>279483.78835799999</v>
+      </c>
+      <c r="H137">
+        <f t="shared" si="5"/>
+        <v>0.13737781700000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>9</v>
       </c>
@@ -3270,8 +4358,16 @@
       <c r="E138" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G138">
+        <f t="shared" si="4"/>
+        <v>296123.80544879998</v>
+      </c>
+      <c r="H138">
+        <f t="shared" si="5"/>
+        <v>0.13807033799999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>9</v>
       </c>
@@ -3287,8 +4383,16 @@
       <c r="E139" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G139">
+        <f t="shared" si="4"/>
+        <v>312227.04775800003</v>
+      </c>
+      <c r="H139">
+        <f t="shared" si="5"/>
+        <v>0.13816927000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -3304,8 +4408,16 @@
       <c r="E140" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G140">
+        <f t="shared" si="4"/>
+        <v>324956.27742960001</v>
+      </c>
+      <c r="H140">
+        <f t="shared" si="5"/>
+        <v>0.13864979499999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>9</v>
       </c>
@@ -3321,8 +4433,16 @@
       <c r="E141" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G141">
+        <f t="shared" si="4"/>
+        <v>342593.16184680001</v>
+      </c>
+      <c r="H141">
+        <f t="shared" si="5"/>
+        <v>0.139215118</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>9</v>
       </c>
@@ -3338,8 +4458,16 @@
       <c r="E142" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G142">
+        <f t="shared" si="4"/>
+        <v>354632.25252600003</v>
+      </c>
+      <c r="H142">
+        <f t="shared" si="5"/>
+        <v>0.13935644899999999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>9</v>
       </c>
@@ -3355,8 +4483,16 @@
       <c r="E143" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G143">
+        <f t="shared" si="4"/>
+        <v>366119.23211640003</v>
+      </c>
+      <c r="H143">
+        <f t="shared" si="5"/>
+        <v>0.13951474</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -3372,8 +4508,16 @@
       <c r="E144" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G144">
+        <f t="shared" si="4"/>
+        <v>384870.56312039995</v>
+      </c>
+      <c r="H144">
+        <f t="shared" si="5"/>
+        <v>0.140065459</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>9</v>
       </c>
@@ -3389,8 +4533,16 @@
       <c r="E145" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G145">
+        <f t="shared" si="4"/>
+        <v>395427.13312440005</v>
+      </c>
+      <c r="H145">
+        <f t="shared" si="5"/>
+        <v>0.140543629</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>9</v>
       </c>
@@ -3406,8 +4558,16 @@
       <c r="E146" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G146">
+        <f t="shared" si="4"/>
+        <v>406699.40274960001</v>
+      </c>
+      <c r="H146">
+        <f t="shared" si="5"/>
+        <v>0.140593094</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>9</v>
       </c>
@@ -3423,8 +4583,16 @@
       <c r="E147" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G147">
+        <f t="shared" si="4"/>
+        <v>420297.6962532</v>
+      </c>
+      <c r="H147">
+        <f t="shared" si="5"/>
+        <v>0.14140103600000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>9</v>
       </c>
@@ -3440,8 +4608,16 @@
       <c r="E148" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G148">
+        <f t="shared" si="4"/>
+        <v>432196.20303600002</v>
+      </c>
+      <c r="H148">
+        <f t="shared" si="5"/>
+        <v>0.14168134199999999</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>9</v>
       </c>
@@ -3457,8 +4633,16 @@
       <c r="E149" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G149">
+        <f t="shared" si="4"/>
+        <v>446420.73378480005</v>
+      </c>
+      <c r="H149">
+        <f t="shared" si="5"/>
+        <v>0.14199462600000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>9</v>
       </c>
@@ -3474,8 +4658,16 @@
       <c r="E150" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G150">
+        <f t="shared" si="4"/>
+        <v>457871.92833720002</v>
+      </c>
+      <c r="H150">
+        <f t="shared" si="5"/>
+        <v>0.14258821599999999</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>9</v>
       </c>
@@ -3491,8 +4683,16 @@
       <c r="E151" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G151">
+        <f t="shared" si="4"/>
+        <v>473796.2457192</v>
+      </c>
+      <c r="H151">
+        <f t="shared" si="5"/>
+        <v>0.14324776</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>9</v>
       </c>
@@ -3508,8 +4708,16 @@
       <c r="E152" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G152">
+        <f t="shared" si="4"/>
+        <v>486499.91467439994</v>
+      </c>
+      <c r="H152">
+        <f t="shared" si="5"/>
+        <v>0.14364348599999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>9</v>
       </c>
@@ -3525,8 +4733,16 @@
       <c r="E153" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G153">
+        <f t="shared" si="4"/>
+        <v>511638.86519400001</v>
+      </c>
+      <c r="H153">
+        <f t="shared" si="5"/>
+        <v>0.144253565</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>9</v>
       </c>
@@ -3542,8 +4758,16 @@
       <c r="E154" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G154">
+        <f t="shared" si="4"/>
+        <v>522284.897574</v>
+      </c>
+      <c r="H154">
+        <f t="shared" si="5"/>
+        <v>0.14443493900000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>9</v>
       </c>
@@ -3559,8 +4783,16 @@
       <c r="E155" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G155">
+        <f t="shared" si="4"/>
+        <v>536867.2781772</v>
+      </c>
+      <c r="H155">
+        <f t="shared" si="5"/>
+        <v>0.14395677000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>9</v>
       </c>
@@ -3576,8 +4808,16 @@
       <c r="E156" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G156">
+        <f t="shared" si="4"/>
+        <v>549347.29092960001</v>
+      </c>
+      <c r="H156">
+        <f t="shared" si="5"/>
+        <v>0.143610509</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>9</v>
       </c>
@@ -3593,8 +4833,16 @@
       <c r="E157" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G157">
+        <f t="shared" si="4"/>
+        <v>561156.33533639996</v>
+      </c>
+      <c r="H157">
+        <f t="shared" si="5"/>
+        <v>0.14249752800000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
         <v>9</v>
       </c>
@@ -3610,8 +4858,16 @@
       <c r="E158" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G158">
+        <f t="shared" si="4"/>
+        <v>570773.54951640009</v>
+      </c>
+      <c r="H158">
+        <f t="shared" si="5"/>
+        <v>0.14077446900000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
         <v>9</v>
       </c>
@@ -3627,8 +4883,16 @@
       <c r="E159" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G159">
+        <f t="shared" si="4"/>
+        <v>578467.3208604001</v>
+      </c>
+      <c r="H159">
+        <f t="shared" si="5"/>
+        <v>0.13854521</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
         <v>9</v>
       </c>
@@ -3644,8 +4908,16 @@
       <c r="E160" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G160">
+        <f t="shared" si="4"/>
+        <v>584371.84302000003</v>
+      </c>
+      <c r="H160">
+        <f t="shared" si="5"/>
+        <v>0.13609170500000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
         <v>9</v>
       </c>
@@ -3661,8 +4933,16 @@
       <c r="E161" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G161">
+        <f t="shared" si="4"/>
+        <v>589739.59048560006</v>
+      </c>
+      <c r="H161">
+        <f t="shared" si="5"/>
+        <v>0.13371734599999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
         <v>9</v>
       </c>
@@ -3678,8 +4958,16 @@
       <c r="E162" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G162">
+        <f t="shared" si="4"/>
+        <v>594570.56316959998</v>
+      </c>
+      <c r="H162">
+        <f t="shared" si="5"/>
+        <v>0.130973642</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
         <v>9</v>
       </c>
@@ -3695,8 +4983,16 @@
       <c r="E163" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G163">
+        <f t="shared" si="4"/>
+        <v>598251.3042288</v>
+      </c>
+      <c r="H163">
+        <f t="shared" si="5"/>
+        <v>0.128233708</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
         <v>9</v>
       </c>
@@ -3712,8 +5008,16 @@
       <c r="E164" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G164">
+        <f t="shared" si="4"/>
+        <v>601011.8601107999</v>
+      </c>
+      <c r="H164">
+        <f t="shared" si="5"/>
+        <v>0.12552580799999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
         <v>9</v>
       </c>
@@ -3729,8 +5033,16 @@
       <c r="E165" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G165">
+        <f t="shared" si="4"/>
+        <v>604232.50853760005</v>
+      </c>
+      <c r="H165">
+        <f t="shared" si="5"/>
+        <v>0.123052517</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
         <v>9</v>
       </c>
@@ -3746,8 +5058,16 @@
       <c r="E166" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G166">
+        <f t="shared" si="4"/>
+        <v>606379.60748879996</v>
+      </c>
+      <c r="H166">
+        <f t="shared" si="5"/>
+        <v>0.120608906</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
         <v>9</v>
       </c>
@@ -3763,8 +5083,16 @@
       <c r="E167" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G167">
+        <f t="shared" si="4"/>
+        <v>608526.70652759995</v>
+      </c>
+      <c r="H167">
+        <f t="shared" si="5"/>
+        <v>0.11833347800000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
         <v>9</v>
       </c>
@@ -3780,8 +5108,16 @@
       <c r="E168" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G168">
+        <f t="shared" si="4"/>
+        <v>610673.80547879997</v>
+      </c>
+      <c r="H168">
+        <f t="shared" si="5"/>
+        <v>0.11588492</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
         <v>9</v>
       </c>
@@ -3797,8 +5133,16 @@
       <c r="E169" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G169">
+        <f t="shared" si="4"/>
+        <v>612820.90443</v>
+      </c>
+      <c r="H169">
+        <f t="shared" si="5"/>
+        <v>0.113386897</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
         <v>9</v>
       </c>
@@ -3814,8 +5158,16 @@
       <c r="E170" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G170">
+        <f t="shared" si="4"/>
+        <v>614968.00338120013</v>
+      </c>
+      <c r="H170">
+        <f t="shared" si="5"/>
+        <v>0.110789942</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
         <v>9</v>
       </c>
@@ -3831,8 +5183,16 @@
       <c r="E171" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G171">
+        <f t="shared" si="4"/>
+        <v>617115.10241999989</v>
+      </c>
+      <c r="H171">
+        <f t="shared" si="5"/>
+        <v>0.108316651</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
         <v>9</v>
       </c>
@@ -3848,8 +5208,16 @@
       <c r="E172" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G172">
+        <f t="shared" si="4"/>
+        <v>619262.20137119992</v>
+      </c>
+      <c r="H172">
+        <f t="shared" si="5"/>
+        <v>0.105818627</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
         <v>9</v>
       </c>
@@ -3865,8 +5233,16 @@
       <c r="E173" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G173">
+        <f t="shared" si="4"/>
+        <v>621409.30032240006</v>
+      </c>
+      <c r="H173">
+        <f t="shared" si="5"/>
+        <v>0.103518467</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
         <v>9</v>
       </c>
@@ -3882,8 +5258,16 @@
       <c r="E174" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G174">
+        <f t="shared" si="4"/>
+        <v>623556.39936119993</v>
+      </c>
+      <c r="H174">
+        <f t="shared" si="5"/>
+        <v>0.101317238</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
         <v>9</v>
       </c>
@@ -3899,8 +5283,16 @@
       <c r="E175" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G175">
+        <f t="shared" si="4"/>
+        <v>625703.49831239996</v>
+      </c>
+      <c r="H175">
+        <f t="shared" si="5"/>
+        <v>9.8952771999999994E-2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
         <v>9</v>
       </c>
@@ -3916,8 +5308,16 @@
       <c r="E176" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G176">
+        <f t="shared" si="4"/>
+        <v>628494.72698399995</v>
+      </c>
+      <c r="H176">
+        <f t="shared" si="5"/>
+        <v>9.6380549999999995E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
         <v>9</v>
       </c>
@@ -3933,8 +5333,16 @@
       <c r="E177" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G177">
+        <f t="shared" si="4"/>
+        <v>632681.56994760002</v>
+      </c>
+      <c r="H177">
+        <f t="shared" si="5"/>
+        <v>9.3847899999999998E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
         <v>9</v>
       </c>
@@ -3950,8 +5358,16 @@
       <c r="E178" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G178">
+        <f t="shared" si="4"/>
+        <v>636975.76793759991</v>
+      </c>
+      <c r="H178">
+        <f t="shared" si="5"/>
+        <v>9.1473541000000005E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
         <v>9</v>
       </c>
@@ -3967,8 +5383,16 @@
       <c r="E179" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G179">
+        <f t="shared" si="4"/>
+        <v>643033.654308</v>
+      </c>
+      <c r="H179">
+        <f t="shared" si="5"/>
+        <v>8.8887186000000007E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
         <v>9</v>
       </c>
@@ -3984,8 +5408,16 @@
       <c r="E180" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G180">
+        <f t="shared" si="4"/>
+        <v>652303.66895399999</v>
+      </c>
+      <c r="H180">
+        <f t="shared" si="5"/>
+        <v>8.6614898999999995E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
         <v>9</v>
       </c>
@@ -4001,8 +5433,16 @@
       <c r="E181" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G181">
+        <f t="shared" si="4"/>
+        <v>662919.88054200006</v>
+      </c>
+      <c r="H181">
+        <f t="shared" si="5"/>
+        <v>8.4630770999999994E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -4018,8 +5458,16 @@
       <c r="E182" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G182">
+        <f t="shared" si="4"/>
+        <v>676428.71158200002</v>
+      </c>
+      <c r="H182">
+        <f t="shared" si="5"/>
+        <v>8.3311681999999998E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
         <v>9</v>
       </c>
@@ -4035,8 +5483,16 @@
       <c r="E183" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G183">
+        <f t="shared" si="4"/>
+        <v>689042.91807359993</v>
+      </c>
+      <c r="H183">
+        <f t="shared" si="5"/>
+        <v>8.2075037000000003E-2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
         <v>9</v>
       </c>
@@ -4052,8 +5508,16 @@
       <c r="E184" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G184">
+        <f t="shared" si="4"/>
+        <v>700851.96248039999</v>
+      </c>
+      <c r="H184">
+        <f t="shared" si="5"/>
+        <v>8.1052742999999997E-2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
         <v>9</v>
       </c>
@@ -4069,8 +5533,16 @@
       <c r="E185" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G185">
+        <f t="shared" si="4"/>
+        <v>713018.856654</v>
+      </c>
+      <c r="H185">
+        <f t="shared" si="5"/>
+        <v>7.9997472999999999E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
         <v>9</v>
       </c>
@@ -4086,8 +5558,16 @@
       <c r="E186" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G186">
+        <f t="shared" si="4"/>
+        <v>724470.05120639992</v>
+      </c>
+      <c r="H186">
+        <f t="shared" si="5"/>
+        <v>7.9074111000000002E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
         <v>9</v>
       </c>
@@ -4103,8 +5583,16 @@
       <c r="E187" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G187">
+        <f t="shared" si="4"/>
+        <v>736279.09552560002</v>
+      </c>
+      <c r="H187">
+        <f t="shared" si="5"/>
+        <v>7.8018840000000006E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
         <v>9</v>
       </c>
@@ -4120,8 +5608,16 @@
       <c r="E188" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G188">
+        <f t="shared" si="4"/>
+        <v>750235.23888359999</v>
+      </c>
+      <c r="H188">
+        <f t="shared" si="5"/>
+        <v>7.6831660999999996E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -4137,8 +5633,16 @@
       <c r="E189" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G189">
+        <f t="shared" si="4"/>
+        <v>763117.83276599995</v>
+      </c>
+      <c r="H189">
+        <f t="shared" si="5"/>
+        <v>7.5644481E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -4154,8 +5658,16 @@
       <c r="E190" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G190">
+        <f t="shared" si="4"/>
+        <v>779221.07507520006</v>
+      </c>
+      <c r="H190">
+        <f t="shared" si="5"/>
+        <v>7.4061575000000004E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
         <v>9</v>
       </c>
@@ -4171,8 +5683,16 @@
       <c r="E191" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G191">
+        <f t="shared" si="4"/>
+        <v>791244.82935960009</v>
+      </c>
+      <c r="H191">
+        <f t="shared" si="5"/>
+        <v>7.2874394999999995E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
         <v>9</v>
       </c>
@@ -4188,8 +5708,16 @@
       <c r="E192" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G192">
+        <f t="shared" si="4"/>
+        <v>804717.87544920004</v>
+      </c>
+      <c r="H192">
+        <f t="shared" si="5"/>
+        <v>7.1489353000000005E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
         <v>9</v>
       </c>
@@ -4205,8 +5733,16 @@
       <c r="E193" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G193">
+        <f t="shared" si="4"/>
+        <v>817654.14675720001</v>
+      </c>
+      <c r="H193">
+        <f t="shared" si="5"/>
+        <v>7.0143883000000004E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
         <v>9</v>
       </c>
@@ -4222,8 +5758,16 @@
       <c r="E194" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G194">
+        <f t="shared" ref="G194:G235" si="6">C194*24*365</f>
+        <v>830214.67573560006</v>
+      </c>
+      <c r="H194">
+        <f t="shared" ref="H194:H234" si="7">D194</f>
+        <v>6.8818198999999997E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -4239,8 +5783,16 @@
       <c r="E195" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G195">
+        <f t="shared" si="6"/>
+        <v>842560.49492400012</v>
+      </c>
+      <c r="H195">
+        <f t="shared" si="7"/>
+        <v>6.7532088000000004E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
         <v>9</v>
       </c>
@@ -4256,8 +5808,16 @@
       <c r="E196" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G196">
+        <f t="shared" si="6"/>
+        <v>855800.93857320002</v>
+      </c>
+      <c r="H196">
+        <f t="shared" si="7"/>
+        <v>6.6147045000000002E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -4273,8 +5833,16 @@
       <c r="E197" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G197">
+        <f t="shared" si="6"/>
+        <v>867967.83274680004</v>
+      </c>
+      <c r="H197">
+        <f t="shared" si="7"/>
+        <v>6.4893910999999999E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -4290,8 +5858,16 @@
       <c r="E198" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G198">
+        <f t="shared" si="6"/>
+        <v>873693.43006679998</v>
+      </c>
+      <c r="H198">
+        <f t="shared" si="7"/>
+        <v>6.4366275000000001E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
         <v>9</v>
       </c>
@@ -4307,8 +5883,16 @@
       <c r="E199" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G199">
+        <f t="shared" si="6"/>
+        <v>512444.02727880009</v>
+      </c>
+      <c r="H199">
+        <f t="shared" si="7"/>
+        <v>0.14370944099999999</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
         <v>9</v>
       </c>
@@ -4324,8 +5908,16 @@
       <c r="E200" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G200">
+        <f t="shared" si="6"/>
+        <v>533531.60657040006</v>
+      </c>
+      <c r="H200">
+        <f t="shared" si="7"/>
+        <v>0.14322891600000001</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -4341,8 +5933,16 @@
       <c r="E201" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G201">
+        <f t="shared" si="6"/>
+        <v>547334.38562999992</v>
+      </c>
+      <c r="H201">
+        <f t="shared" si="7"/>
+        <v>0.14199462600000001</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -4358,8 +5958,16 @@
       <c r="E202" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G202">
+        <f t="shared" si="6"/>
+        <v>556352.20136519999</v>
+      </c>
+      <c r="H202">
+        <f t="shared" si="7"/>
+        <v>0.140543629</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
         <v>9</v>
       </c>
@@ -4375,8 +5983,16 @@
       <c r="E203" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G203">
+        <f t="shared" si="6"/>
+        <v>563974.40272080002</v>
+      </c>
+      <c r="H203">
+        <f t="shared" si="7"/>
+        <v>0.138466064</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
         <v>9</v>
       </c>
@@ -4392,8 +6008,16 @@
       <c r="E204" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G204">
+        <f t="shared" si="6"/>
+        <v>569878.92488040007</v>
+      </c>
+      <c r="H204">
+        <f t="shared" si="7"/>
+        <v>0.13630935499999999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -4409,8 +6033,16 @@
       <c r="E205" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G205">
+        <f t="shared" si="6"/>
+        <v>575246.67234599998</v>
+      </c>
+      <c r="H205">
+        <f t="shared" si="7"/>
+        <v>0.133862446</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
         <v>9</v>
       </c>
@@ -4426,8 +6058,16 @@
       <c r="E206" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G206">
+        <f t="shared" si="6"/>
+        <v>579540.87033599999</v>
+      </c>
+      <c r="H206">
+        <f t="shared" si="7"/>
+        <v>0.131145124</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -4443,8 +6083,16 @@
       <c r="E207" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G207">
+        <f t="shared" si="6"/>
+        <v>582761.51876279991</v>
+      </c>
+      <c r="H207">
+        <f t="shared" si="7"/>
+        <v>0.128968628</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -4460,8 +6108,16 @@
       <c r="E208" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G208">
+        <f t="shared" si="6"/>
+        <v>585982.16727720003</v>
+      </c>
+      <c r="H208">
+        <f t="shared" si="7"/>
+        <v>0.126363429</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
         <v>9</v>
       </c>
@@ -4477,8 +6133,16 @@
       <c r="E209" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G209">
+        <f t="shared" si="6"/>
+        <v>589202.81570399995</v>
+      </c>
+      <c r="H209">
+        <f t="shared" si="7"/>
+        <v>0.123648305</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
         <v>9</v>
       </c>
@@ -4494,8 +6158,16 @@
       <c r="E210" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G210">
+        <f t="shared" si="6"/>
+        <v>592423.46413079998</v>
+      </c>
+      <c r="H210">
+        <f t="shared" si="7"/>
+        <v>0.12011424800000001</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
         <v>9</v>
       </c>
@@ -4511,8 +6183,16 @@
       <c r="E211" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G211">
+        <f t="shared" si="6"/>
+        <v>595644.11264519999</v>
+      </c>
+      <c r="H211">
+        <f t="shared" si="7"/>
+        <v>0.116459274</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
         <v>9</v>
       </c>
@@ -4528,8 +6208,16 @@
       <c r="E212" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G212">
+        <f t="shared" si="6"/>
+        <v>598327.986378</v>
+      </c>
+      <c r="H212">
+        <f t="shared" si="7"/>
+        <v>0.113782623</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
         <v>9</v>
       </c>
@@ -4545,8 +6233,16 @@
       <c r="E213" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G213">
+        <f t="shared" si="6"/>
+        <v>601011.8601107999</v>
+      </c>
+      <c r="H213">
+        <f t="shared" si="7"/>
+        <v>0.110871678</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
         <v>9</v>
       </c>
@@ -4562,8 +6258,16 @@
       <c r="E214" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G214">
+        <f t="shared" si="6"/>
+        <v>604232.50853760005</v>
+      </c>
+      <c r="H214">
+        <f t="shared" si="7"/>
+        <v>0.107043181</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
         <v>9</v>
       </c>
@@ -4579,8 +6283,16 @@
       <c r="E215" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G215">
+        <f t="shared" si="6"/>
+        <v>607453.15696439997</v>
+      </c>
+      <c r="H215">
+        <f t="shared" si="7"/>
+        <v>0.103279382</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -4596,8 +6308,16 @@
       <c r="E216" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G216">
+        <f t="shared" si="6"/>
+        <v>610673.80547879997</v>
+      </c>
+      <c r="H216">
+        <f t="shared" si="7"/>
+        <v>0.10013335700000001</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
         <v>9</v>
       </c>
@@ -4613,8 +6333,16 @@
       <c r="E217" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G217">
+        <f t="shared" si="6"/>
+        <v>613894.45390560001</v>
+      </c>
+      <c r="H217">
+        <f t="shared" si="7"/>
+        <v>9.7178599000000004E-2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
         <v>9</v>
       </c>
@@ -4630,8 +6358,16 @@
       <c r="E218" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G218">
+        <f t="shared" si="6"/>
+        <v>618188.65189560002</v>
+      </c>
+      <c r="H218">
+        <f t="shared" si="7"/>
+        <v>9.4263413000000004E-2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -4647,8 +6383,16 @@
       <c r="E219" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G219">
+        <f t="shared" si="6"/>
+        <v>623556.39936119993</v>
+      </c>
+      <c r="H219">
+        <f t="shared" si="7"/>
+        <v>9.1275677999999999E-2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
         <v>9</v>
       </c>
@@ -4664,8 +6408,16 @@
       <c r="E220" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G220">
+        <f t="shared" si="6"/>
+        <v>629353.566582</v>
+      </c>
+      <c r="H220">
+        <f t="shared" si="7"/>
+        <v>8.9079396000000005E-2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
         <v>9</v>
       </c>
@@ -4681,8 +6433,16 @@
       <c r="E221" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G221">
+        <f t="shared" si="6"/>
+        <v>634828.66889880004</v>
+      </c>
+      <c r="H221">
+        <f t="shared" si="7"/>
+        <v>8.7615208E-2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
         <v>9</v>
       </c>
@@ -4698,8 +6458,16 @@
       <c r="E222" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G222">
+        <f t="shared" si="6"/>
+        <v>650395.13651400013</v>
+      </c>
+      <c r="H222">
+        <f t="shared" si="7"/>
+        <v>8.4977030999999995E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -4715,8 +6483,16 @@
       <c r="E223" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G223">
+        <f t="shared" si="6"/>
+        <v>664243.9249332</v>
+      </c>
+      <c r="H223">
+        <f t="shared" si="7"/>
+        <v>8.3440292999999999E-2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
         <v>9</v>
       </c>
@@ -4732,8 +6508,16 @@
       <c r="E224" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G224">
+        <f t="shared" si="6"/>
+        <v>677663.29350959999</v>
+      </c>
+      <c r="H224">
+        <f t="shared" si="7"/>
+        <v>8.2243221000000005E-2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -4749,8 +6533,16 @@
       <c r="E225" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G225">
+        <f t="shared" si="6"/>
+        <v>688371.94964040001</v>
+      </c>
+      <c r="H225">
+        <f t="shared" si="7"/>
+        <v>8.1333050000000004E-2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
         <v>9</v>
       </c>
@@ -4766,8 +6558,16 @@
       <c r="E226" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G226">
+        <f t="shared" si="6"/>
+        <v>702569.64167640009</v>
+      </c>
+      <c r="H226">
+        <f t="shared" si="7"/>
+        <v>8.0155763000000005E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
         <v>9</v>
       </c>
@@ -4783,8 +6583,16 @@
       <c r="E227" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G227">
+        <f t="shared" si="6"/>
+        <v>716418.430008</v>
+      </c>
+      <c r="H227">
+        <f t="shared" si="7"/>
+        <v>7.9107088000000006E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
         <v>9</v>
       </c>
@@ -4800,8 +6608,16 @@
       <c r="E228" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G228">
+        <f t="shared" si="6"/>
+        <v>176399.999988</v>
+      </c>
+      <c r="H228">
+        <f t="shared" si="7"/>
+        <v>0.135023697</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
         <v>9</v>
       </c>
@@ -4817,8 +6633,16 @@
       <c r="E229" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G229">
+        <f t="shared" si="6"/>
+        <v>444600.00002159999</v>
+      </c>
+      <c r="H229">
+        <f t="shared" si="7"/>
+        <v>0.14199052100000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
         <v>9</v>
       </c>
@@ -4834,8 +6658,16 @@
       <c r="E230" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G230">
+        <f t="shared" si="6"/>
+        <v>489600.00000959996</v>
+      </c>
+      <c r="H230">
+        <f t="shared" si="7"/>
+        <v>0.143317536</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
         <v>9</v>
       </c>
@@ -4851,8 +6683,16 @@
       <c r="E231" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G231">
+        <f t="shared" si="6"/>
+        <v>466199.99998079997</v>
+      </c>
+      <c r="H231">
+        <f t="shared" si="7"/>
+        <v>0.14265402799999999</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
         <v>9</v>
       </c>
@@ -4868,8 +6708,16 @@
       <c r="E232" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G232">
+        <f t="shared" si="6"/>
+        <v>752400.00000959996</v>
+      </c>
+      <c r="H232">
+        <f t="shared" si="7"/>
+        <v>7.6303317999999995E-2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
         <v>9</v>
       </c>
@@ -4885,8 +6733,16 @@
       <c r="E233" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G233">
+        <f t="shared" si="6"/>
+        <v>844199.99996759999</v>
+      </c>
+      <c r="H233">
+        <f t="shared" si="7"/>
+        <v>6.7014218E-2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -4902,8 +6758,16 @@
       <c r="E234" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G234">
+        <f t="shared" si="6"/>
+        <v>874800.00001199997</v>
+      </c>
+      <c r="H234">
+        <f t="shared" si="7"/>
+        <v>6.4028435999999994E-2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
         <v>10</v>
       </c>
@@ -4919,8 +6783,16 @@
       <c r="E235" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G235">
+        <f t="shared" si="6"/>
+        <v>183121.13442839999</v>
+      </c>
+      <c r="H235">
+        <f>D235/4514*1000/1000*10000</f>
+        <v>2.9233432609658836</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -4936,8 +6808,16 @@
       <c r="E236" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G236">
+        <f t="shared" ref="G236:G299" si="8">C236*24*365</f>
+        <v>193760.64971880004</v>
+      </c>
+      <c r="H236">
+        <f t="shared" ref="H236:H299" si="9">D236/4514*1000/1000*10000</f>
+        <v>2.9433980859548075</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
         <v>10</v>
       </c>
@@ -4953,8 +6833,16 @@
       <c r="E237" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G237">
+        <f t="shared" si="8"/>
+        <v>205438.16649240002</v>
+      </c>
+      <c r="H237">
+        <f t="shared" si="9"/>
+        <v>2.9672279397430219</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
         <v>10</v>
       </c>
@@ -4970,8 +6858,16 @@
       <c r="E238" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G238">
+        <f t="shared" si="8"/>
+        <v>217375.18363680001</v>
+      </c>
+      <c r="H238">
+        <f t="shared" si="9"/>
+        <v>2.9932670403190076</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
         <v>10</v>
       </c>
@@ -4987,8 +6883,16 @@
       <c r="E239" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G239">
+        <f t="shared" si="8"/>
+        <v>228051.77045880002</v>
+      </c>
+      <c r="H239">
+        <f t="shared" si="9"/>
+        <v>3.0143483562250775</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
         <v>10</v>
       </c>
@@ -5004,8 +6908,16 @@
       <c r="E240" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G240">
+        <f t="shared" si="8"/>
+        <v>240730.21718400001</v>
+      </c>
+      <c r="H240">
+        <f t="shared" si="9"/>
+        <v>3.043200341160833</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
         <v>10</v>
       </c>
@@ -5021,8 +6933,16 @@
       <c r="E241" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G241">
+        <f t="shared" si="8"/>
+        <v>252667.23432839997</v>
+      </c>
+      <c r="H241">
+        <f t="shared" si="9"/>
+        <v>3.070674142667257</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -5038,8 +6958,16 @@
       <c r="E242" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G242">
+        <f t="shared" si="8"/>
+        <v>264604.25156040001</v>
+      </c>
+      <c r="H242">
+        <f t="shared" si="9"/>
+        <v>3.0969944638901192</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -5055,8 +6983,16 @@
       <c r="E243" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G243">
+        <f t="shared" si="8"/>
+        <v>276541.26870479999</v>
+      </c>
+      <c r="H243">
+        <f t="shared" si="9"/>
+        <v>3.1272995347806822</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
         <v>10</v>
       </c>
@@ -5072,8 +7008,16 @@
       <c r="E244" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G244">
+        <f t="shared" si="8"/>
+        <v>289227.95359679998</v>
+      </c>
+      <c r="H244">
+        <f t="shared" si="9"/>
+        <v>3.1577094683207796</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
         <v>10</v>
       </c>
@@ -5089,8 +7033,16 @@
       <c r="E245" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G245">
+        <f t="shared" si="8"/>
+        <v>301141.90399680001</v>
+      </c>
+      <c r="H245">
+        <f t="shared" si="9"/>
+        <v>3.1875950908285335</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -5106,8 +7058,16 @@
       <c r="E246" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G246">
+        <f t="shared" si="8"/>
+        <v>312482.07036719995</v>
+      </c>
+      <c r="H246">
+        <f t="shared" si="9"/>
+        <v>3.2176773305272484</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
         <v>10</v>
       </c>
@@ -5123,8 +7083,16 @@
       <c r="E247" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G247">
+        <f t="shared" si="8"/>
+        <v>324289.3372824</v>
+      </c>
+      <c r="H247">
+        <f t="shared" si="9"/>
+        <v>3.2476523260965888</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -5140,8 +7108,16 @@
       <c r="E248" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G248">
+        <f t="shared" si="8"/>
+        <v>335707.35368519998</v>
+      </c>
+      <c r="H248">
+        <f t="shared" si="9"/>
+        <v>3.2806838037217543</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -5157,8 +7133,16 @@
       <c r="E249" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G249">
+        <f t="shared" si="8"/>
+        <v>348394.03857719997</v>
+      </c>
+      <c r="H249">
+        <f t="shared" si="9"/>
+        <v>3.3165751506424459</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -5174,8 +7158,16 @@
       <c r="E250" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G250">
+        <f t="shared" si="8"/>
+        <v>360411.78919560002</v>
+      </c>
+      <c r="H250">
+        <f t="shared" si="9"/>
+        <v>3.3518087284005316</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
         <v>10</v>
       </c>
@@ -5191,8 +7183,16 @@
       <c r="E251" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G251">
+        <f t="shared" si="8"/>
+        <v>372037.40594759997</v>
+      </c>
+      <c r="H251">
+        <f t="shared" si="9"/>
+        <v>3.3857839654408508</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
         <v>10</v>
       </c>
@@ -5208,8 +7208,16 @@
       <c r="E252" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G252">
+        <f t="shared" si="8"/>
+        <v>384262.75682760001</v>
+      </c>
+      <c r="H252">
+        <f t="shared" si="9"/>
+        <v>3.4287773172352685</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
         <v>10</v>
       </c>
@@ -5225,8 +7233,16 @@
       <c r="E253" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G253">
+        <f t="shared" si="8"/>
+        <v>394873.43875320005</v>
+      </c>
+      <c r="H253">
+        <f t="shared" si="9"/>
+        <v>3.4608555073105891</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -5242,8 +7258,16 @@
       <c r="E254" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G254">
+        <f t="shared" si="8"/>
+        <v>406291.45515600004</v>
+      </c>
+      <c r="H254">
+        <f t="shared" si="9"/>
+        <v>3.4981767877713779</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
         <v>10</v>
       </c>
@@ -5259,8 +7283,16 @@
       <c r="E255" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G255">
+        <f t="shared" si="8"/>
+        <v>418747.47304200003</v>
+      </c>
+      <c r="H255">
+        <f t="shared" si="9"/>
+        <v>3.5419327735932651</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
         <v>10</v>
       </c>
@@ -5276,8 +7308,16 @@
       <c r="E256" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G256">
+        <f t="shared" si="8"/>
+        <v>429819.48897960002</v>
+      </c>
+      <c r="H256">
+        <f t="shared" si="9"/>
+        <v>3.5813512915374388</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -5293,8 +7333,16 @@
       <c r="E257" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G257">
+        <f t="shared" si="8"/>
+        <v>442506.17387160001</v>
+      </c>
+      <c r="H257">
+        <f t="shared" si="9"/>
+        <v>3.6269661918475857</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -5310,8 +7358,16 @@
       <c r="E258" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G258">
+        <f t="shared" si="8"/>
+        <v>455077.52521679999</v>
+      </c>
+      <c r="H258">
+        <f t="shared" si="9"/>
+        <v>3.6765789477182098</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
         <v>10</v>
       </c>
@@ -5327,8 +7383,16 @@
       <c r="E259" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G259">
+        <f t="shared" si="8"/>
+        <v>466034.20769520005</v>
+      </c>
+      <c r="H259">
+        <f t="shared" si="9"/>
+        <v>3.7176716814355339</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
         <v>10</v>
       </c>
@@ -5344,8 +7408,16 @@
       <c r="E260" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G260">
+        <f t="shared" si="8"/>
+        <v>476298.88906799996</v>
+      </c>
+      <c r="H260">
+        <f t="shared" si="9"/>
+        <v>3.7611893420469649</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
         <v>10</v>
       </c>
@@ -5361,8 +7433,16 @@
       <c r="E261" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G261">
+        <f t="shared" si="8"/>
+        <v>490369.57599600003</v>
+      </c>
+      <c r="H261">
+        <f t="shared" si="9"/>
+        <v>3.8199119716437751</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -5378,8 +7458,16 @@
       <c r="E262" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G262">
+        <f t="shared" si="8"/>
+        <v>503448.39475440001</v>
+      </c>
+      <c r="H262">
+        <f t="shared" si="9"/>
+        <v>3.8708748249889235</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
         <v>10</v>
       </c>
@@ -5395,8 +7483,16 @@
       <c r="E263" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G263">
+        <f t="shared" si="8"/>
+        <v>520175.04736919998</v>
+      </c>
+      <c r="H263">
+        <f t="shared" si="9"/>
+        <v>3.9284439743021711</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
         <v>10</v>
       </c>
@@ -5412,8 +7508,16 @@
       <c r="E264" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G264">
+        <f t="shared" si="8"/>
+        <v>531889.63567440002</v>
+      </c>
+      <c r="H264">
+        <f t="shared" si="9"/>
+        <v>3.9619044328754982</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
         <v>10</v>
       </c>
@@ -5429,8 +7533,16 @@
       <c r="E265" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G265">
+        <f t="shared" si="8"/>
+        <v>543307.65207720001</v>
+      </c>
+      <c r="H265">
+        <f t="shared" si="9"/>
+        <v>3.9786346632698271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
         <v>10</v>
       </c>
@@ -5446,8 +7558,16 @@
       <c r="E266" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G266">
+        <f t="shared" si="8"/>
+        <v>554725.66847999999</v>
+      </c>
+      <c r="H266">
+        <f t="shared" si="9"/>
+        <v>3.9679101572884359</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
         <v>10</v>
       </c>
@@ -5463,8 +7583,16 @@
       <c r="E267" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G267">
+        <f t="shared" si="8"/>
+        <v>566143.68488279998</v>
+      </c>
+      <c r="H267">
+        <f t="shared" si="9"/>
+        <v>3.9138586464333183</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
         <v>10</v>
       </c>
@@ -5480,8 +7608,16 @@
       <c r="E268" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G268">
+        <f t="shared" si="8"/>
+        <v>575485.69831919996</v>
+      </c>
+      <c r="H268">
+        <f t="shared" si="9"/>
+        <v>3.819237859991139</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
         <v>10</v>
       </c>
@@ -5497,8 +7633,16 @@
       <c r="E269" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G269">
+        <f t="shared" si="8"/>
+        <v>581713.70721839997</v>
+      </c>
+      <c r="H269">
+        <f t="shared" si="9"/>
+        <v>3.7142112405848473</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
         <v>10</v>
       </c>
@@ -5514,8 +7658,16 @@
       <c r="E270" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G270">
+        <f t="shared" si="8"/>
+        <v>586384.71398039989</v>
+      </c>
+      <c r="H270">
+        <f t="shared" si="9"/>
+        <v>3.606387055826318</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
         <v>10</v>
       </c>
@@ -5531,8 +7683,16 @@
       <c r="E271" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G271">
+        <f t="shared" si="8"/>
+        <v>590017.71917159995</v>
+      </c>
+      <c r="H271">
+        <f t="shared" si="9"/>
+        <v>3.505326459902526</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
         <v>10</v>
       </c>
@@ -5548,8 +7708,16 @@
       <c r="E272" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G272">
+        <f t="shared" si="8"/>
+        <v>593131.72362120007</v>
+      </c>
+      <c r="H272">
+        <f t="shared" si="9"/>
+        <v>3.3999403123615415</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
         <v>10</v>
       </c>
@@ -5565,8 +7733,16 @@
       <c r="E273" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G273">
+        <f t="shared" si="8"/>
+        <v>596245.72815840004</v>
+      </c>
+      <c r="H273">
+        <f t="shared" si="9"/>
+        <v>3.2788248892334959</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
         <v>10</v>
       </c>
@@ -5582,8 +7758,16 @@
       <c r="E274" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G274">
+        <f t="shared" si="8"/>
+        <v>598840.73186639999</v>
+      </c>
+      <c r="H274">
+        <f t="shared" si="9"/>
+        <v>3.1640011785556048</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
         <v>10</v>
       </c>
@@ -5599,8 +7783,16 @@
       <c r="E275" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G275">
+        <f t="shared" si="8"/>
+        <v>600916.73483279999</v>
+      </c>
+      <c r="H275">
+        <f t="shared" si="9"/>
+        <v>3.062547350465219</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
         <v>10</v>
       </c>
@@ -5616,8 +7808,16 @@
       <c r="E276" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G276">
+        <f t="shared" si="8"/>
+        <v>602992.7377992</v>
+      </c>
+      <c r="H276">
+        <f t="shared" si="9"/>
+        <v>2.954015347806823</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
         <v>10</v>
       </c>
@@ -5633,8 +7833,16 @@
       <c r="E277" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G277">
+        <f t="shared" si="8"/>
+        <v>605068.74085320008</v>
+      </c>
+      <c r="H277">
+        <f t="shared" si="9"/>
+        <v>2.8336863890119632</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
         <v>10</v>
       </c>
@@ -5650,8 +7858,16 @@
       <c r="E278" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G278">
+        <f t="shared" si="8"/>
+        <v>607144.74381959997</v>
+      </c>
+      <c r="H278">
+        <f t="shared" si="9"/>
+        <v>2.7109980394328757</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
         <v>10</v>
       </c>
@@ -5667,8 +7883,16 @@
       <c r="E279" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G279">
+        <f t="shared" si="8"/>
+        <v>609220.74678599997</v>
+      </c>
+      <c r="H279">
+        <f t="shared" si="9"/>
+        <v>2.5717939499335403</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
         <v>10</v>
       </c>
@@ -5684,8 +7908,16 @@
       <c r="E280" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G280">
+        <f t="shared" si="8"/>
+        <v>611123.74947599997</v>
+      </c>
+      <c r="H280">
+        <f t="shared" si="9"/>
+        <v>2.4278710766504208</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
         <v>10</v>
       </c>
@@ -5701,8 +7933,16 @@
       <c r="E281" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G281">
+        <f t="shared" si="8"/>
+        <v>613372.75271879998</v>
+      </c>
+      <c r="H281">
+        <f t="shared" si="9"/>
+        <v>2.2863075963668589</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
         <v>10</v>
       </c>
@@ -5718,8 +7958,16 @@
       <c r="E282" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G282">
+        <f t="shared" si="8"/>
+        <v>614929.75503120001</v>
+      </c>
+      <c r="H282">
+        <f t="shared" si="9"/>
+        <v>2.147103506867523</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
         <v>10</v>
       </c>
@@ -5735,8 +7983,16 @@
       <c r="E283" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G283">
+        <f t="shared" si="8"/>
+        <v>617351.75846280006</v>
+      </c>
+      <c r="H283">
+        <f t="shared" si="9"/>
+        <v>1.9827325764288879</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
         <v>10</v>
       </c>
@@ -5752,8 +8008,16 @@
       <c r="E284" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G284">
+        <f t="shared" si="8"/>
+        <v>619081.7609639999</v>
+      </c>
+      <c r="H284">
+        <f t="shared" si="9"/>
+        <v>1.8616171533008419</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
         <v>10</v>
       </c>
@@ -5769,8 +8033,16 @@
       <c r="E285" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G285">
+        <f t="shared" si="8"/>
+        <v>621157.7639303999</v>
+      </c>
+      <c r="H285">
+        <f t="shared" si="9"/>
+        <v>1.7216266016836508</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
         <v>10</v>
       </c>
@@ -5786,8 +8058,16 @@
       <c r="E286" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G286">
+        <f t="shared" si="8"/>
+        <v>623752.76763840008</v>
+      </c>
+      <c r="H286">
+        <f t="shared" si="9"/>
+        <v>1.5690526273814798</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
         <v>10</v>
       </c>
@@ -5803,8 +8083,16 @@
       <c r="E287" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G287">
+        <f t="shared" si="8"/>
+        <v>625828.77069239994</v>
+      </c>
+      <c r="H287">
+        <f t="shared" si="9"/>
+        <v>1.4487236685866194</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
         <v>10</v>
       </c>
@@ -5820,8 +8108,16 @@
       <c r="E288" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G288">
+        <f t="shared" si="8"/>
+        <v>628423.7744004</v>
+      </c>
+      <c r="H288">
+        <f t="shared" si="9"/>
+        <v>1.3079466504209127</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
         <v>10</v>
       </c>
@@ -5837,8 +8133,16 @@
       <c r="E289" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G289">
+        <f t="shared" si="8"/>
+        <v>631537.77885</v>
+      </c>
+      <c r="H289">
+        <f t="shared" si="9"/>
+        <v>1.1695290252547632</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
         <v>10</v>
       </c>
@@ -5854,8 +8158,16 @@
       <c r="E290" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G290">
+        <f t="shared" si="8"/>
+        <v>634651.78329960001</v>
+      </c>
+      <c r="H290">
+        <f t="shared" si="9"/>
+        <v>1.0515594594594595</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
         <v>10</v>
       </c>
@@ -5871,8 +8183,16 @@
       <c r="E291" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G291">
+        <f t="shared" si="8"/>
+        <v>638284.78857840016</v>
+      </c>
+      <c r="H291">
+        <f t="shared" si="9"/>
+        <v>0.94735300620292417</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
         <v>10</v>
       </c>
@@ -5888,8 +8208,16 @@
       <c r="E292" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G292">
+        <f t="shared" si="8"/>
+        <v>643474.79599439993</v>
+      </c>
+      <c r="H292">
+        <f t="shared" si="9"/>
+        <v>0.83134959902525474</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
         <v>10</v>
       </c>
@@ -5905,8 +8233,16 @@
       <c r="E293" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G293">
+        <f t="shared" si="8"/>
+        <v>651259.80720599997</v>
+      </c>
+      <c r="H293">
+        <f t="shared" si="9"/>
+        <v>0.72072036109880366</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
         <v>10</v>
       </c>
@@ -5922,8 +8258,16 @@
       <c r="E294" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G294">
+        <f t="shared" si="8"/>
+        <v>661639.82212559995</v>
+      </c>
+      <c r="H294">
+        <f t="shared" si="9"/>
+        <v>0.63301773371732384</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
         <v>10</v>
       </c>
@@ -5939,8 +8283,16 @@
       <c r="E295" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G295">
+        <f t="shared" si="8"/>
+        <v>673057.83852839994</v>
+      </c>
+      <c r="H295">
+        <f t="shared" si="9"/>
+        <v>0.57896622286220645</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
         <v>10</v>
       </c>
@@ -5956,8 +8308,16 @@
       <c r="E296" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G296">
+        <f t="shared" si="8"/>
+        <v>683437.85344800004</v>
+      </c>
+      <c r="H296">
+        <f t="shared" si="9"/>
+        <v>0.55084418475852903</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
         <v>10</v>
       </c>
@@ -5973,8 +8333,16 @@
       <c r="E297" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G297">
+        <f t="shared" si="8"/>
+        <v>703901.31138480001</v>
+      </c>
+      <c r="H297">
+        <f t="shared" si="9"/>
+        <v>0.51946053389455027</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
         <v>10</v>
       </c>
@@ -5990,8 +8358,16 @@
       <c r="E298" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G298">
+        <f t="shared" si="8"/>
+        <v>755059.95640200004</v>
+      </c>
+      <c r="H298">
+        <f t="shared" si="9"/>
+        <v>0.49788895657953036</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
         <v>10</v>
       </c>
@@ -6007,8 +8383,16 @@
       <c r="E299" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G299">
+        <f t="shared" si="8"/>
+        <v>766477.97280479991</v>
+      </c>
+      <c r="H299">
+        <f t="shared" si="9"/>
+        <v>0.49788895657953036</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
         <v>10</v>
       </c>
@@ -6024,8 +8408,16 @@
       <c r="E300" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G300">
+        <f t="shared" ref="G300:G363" si="10">C300*24*365</f>
+        <v>777376.98846600007</v>
+      </c>
+      <c r="H300">
+        <f t="shared" ref="H300:H363" si="11">D300/4514*1000/1000*10000</f>
+        <v>0.49788895657953036</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
         <v>10</v>
       </c>
@@ -6041,8 +8433,16 @@
       <c r="E301" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G301">
+        <f t="shared" si="10"/>
+        <v>812150.03841600008</v>
+      </c>
+      <c r="H301">
+        <f t="shared" si="11"/>
+        <v>0.49359915374390784</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
         <v>10</v>
       </c>
@@ -6058,8 +8458,16 @@
       <c r="E302" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G302">
+        <f t="shared" si="10"/>
+        <v>823568.05481879995</v>
+      </c>
+      <c r="H302">
+        <f t="shared" si="11"/>
+        <v>0.48845139122729292</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
         <v>10</v>
       </c>
@@ -6075,8 +8483,16 @@
       <c r="E303" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G303">
+        <f t="shared" si="10"/>
+        <v>834986.07122159994</v>
+      </c>
+      <c r="H303">
+        <f t="shared" si="11"/>
+        <v>0.48845139122729292</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
         <v>10</v>
       </c>
@@ -6092,8 +8508,16 @@
       <c r="E304" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G304">
+        <f t="shared" si="10"/>
+        <v>846404.08762440004</v>
+      </c>
+      <c r="H304">
+        <f t="shared" si="11"/>
+        <v>0.48845139122729292</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
         <v>10</v>
       </c>
@@ -6109,8 +8533,16 @@
       <c r="E305" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G305">
+        <f t="shared" si="10"/>
+        <v>857822.10402720002</v>
+      </c>
+      <c r="H305">
+        <f t="shared" si="11"/>
+        <v>0.48845139122729292</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
         <v>10</v>
       </c>
@@ -6126,8 +8558,16 @@
       <c r="E306" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G306">
+        <f t="shared" si="10"/>
+        <v>869240.12043000001</v>
+      </c>
+      <c r="H306">
+        <f t="shared" si="11"/>
+        <v>0.49016731058927776</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
         <v>10</v>
       </c>
@@ -6143,8 +8583,16 @@
       <c r="E307" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G307">
+        <f t="shared" si="10"/>
+        <v>175780.13248920001</v>
+      </c>
+      <c r="H307">
+        <f t="shared" si="11"/>
+        <v>2.9115766814355339</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
         <v>10</v>
       </c>
@@ -6160,8 +8608,16 @@
       <c r="E308" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G308">
+        <f t="shared" si="10"/>
+        <v>730966.88742360007</v>
+      </c>
+      <c r="H308">
+        <f t="shared" si="11"/>
+        <v>0.50636116304829415</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
         <v>10</v>
       </c>
@@ -6177,8 +8633,16 @@
       <c r="E309" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G309">
+        <f t="shared" si="10"/>
+        <v>797101.98672480008</v>
+      </c>
+      <c r="H309">
+        <f t="shared" si="11"/>
+        <v>0.49053737483385024</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
         <v>10</v>
       </c>
@@ -6194,8 +8658,16 @@
       <c r="E310" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G310">
+        <f t="shared" si="10"/>
+        <v>518395.61621760001</v>
+      </c>
+      <c r="H310">
+        <f t="shared" si="11"/>
+        <v>3.8954124944616746</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
         <v>10</v>
       </c>
@@ -6211,8 +8683,16 @@
       <c r="E311" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G311">
+        <f t="shared" si="10"/>
+        <v>529709.83248959994</v>
+      </c>
+      <c r="H311">
+        <f t="shared" si="11"/>
+        <v>3.9076813314133805</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
         <v>10</v>
       </c>
@@ -6228,8 +8708,16 @@
       <c r="E312" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G312">
+        <f t="shared" si="10"/>
+        <v>541231.6491108</v>
+      </c>
+      <c r="H312">
+        <f t="shared" si="11"/>
+        <v>3.8979863757199826</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
         <v>10</v>
       </c>
@@ -6245,8 +8733,16 @@
       <c r="E313" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G313">
+        <f t="shared" si="10"/>
+        <v>552649.66551359999</v>
+      </c>
+      <c r="H313">
+        <f t="shared" si="11"/>
+        <v>3.840074042977403</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
         <v>10</v>
       </c>
@@ -6262,8 +8758,16 @@
       <c r="E314" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G314">
+        <f t="shared" si="10"/>
+        <v>561991.67894999997</v>
+      </c>
+      <c r="H314">
+        <f t="shared" si="11"/>
+        <v>3.743737337173239</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
         <v>10</v>
       </c>
@@ -6279,8 +8783,16 @@
       <c r="E315" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G315">
+        <f t="shared" si="10"/>
+        <v>568219.68784919998</v>
+      </c>
+      <c r="H315">
+        <f t="shared" si="11"/>
+        <v>3.6368232033673018</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
         <v>10</v>
       </c>
@@ -6296,8 +8808,16 @@
       <c r="E316" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G316">
+        <f t="shared" si="10"/>
+        <v>572890.69461120002</v>
+      </c>
+      <c r="H316">
+        <f t="shared" si="11"/>
+        <v>3.5261677492246344</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
         <v>10</v>
       </c>
@@ -6313,8 +8833,16 @@
       <c r="E317" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G317">
+        <f t="shared" si="10"/>
+        <v>576523.69980239996</v>
+      </c>
+      <c r="H317">
+        <f t="shared" si="11"/>
+        <v>3.4235342268498004</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
         <v>10</v>
       </c>
@@ -6330,8 +8858,16 @@
       <c r="E318" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G318">
+        <f t="shared" si="10"/>
+        <v>579637.70425199997</v>
+      </c>
+      <c r="H318">
+        <f t="shared" si="11"/>
+        <v>3.3165751506424459</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
         <v>10</v>
       </c>
@@ -6347,8 +8883,16 @@
       <c r="E319" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G319">
+        <f t="shared" si="10"/>
+        <v>582751.70870160009</v>
+      </c>
+      <c r="H319">
+        <f t="shared" si="11"/>
+        <v>3.1923138746123172</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
         <v>10</v>
       </c>
@@ -6364,8 +8908,16 @@
       <c r="E320" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G320">
+        <f t="shared" si="10"/>
+        <v>585346.7124972</v>
+      </c>
+      <c r="H320">
+        <f t="shared" si="11"/>
+        <v>3.0814224811696942</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
         <v>10</v>
       </c>
@@ -6381,8 +8933,16 @@
       <c r="E321" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G321">
+        <f t="shared" si="10"/>
+        <v>587422.71546360001</v>
+      </c>
+      <c r="H321">
+        <f t="shared" si="11"/>
+        <v>2.9749128134692069</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
         <v>10</v>
       </c>
@@ -6398,8 +8958,16 @@
       <c r="E322" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G322">
+        <f t="shared" si="10"/>
+        <v>589498.71843000001</v>
+      </c>
+      <c r="H322">
+        <f t="shared" si="11"/>
+        <v>2.8619990850686756</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
         <v>10</v>
       </c>
@@ -6415,8 +8983,16 @@
       <c r="E323" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G323">
+        <f t="shared" si="10"/>
+        <v>591574.72139640001</v>
+      </c>
+      <c r="H323">
+        <f t="shared" si="11"/>
+        <v>2.7345919517058044</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
         <v>10</v>
       </c>
@@ -6432,8 +9008,16 @@
       <c r="E324" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G324">
+        <f t="shared" si="10"/>
+        <v>593650.72445039998</v>
+      </c>
+      <c r="H324">
+        <f t="shared" si="11"/>
+        <v>2.6166223859105004</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
         <v>10</v>
       </c>
@@ -6449,8 +9033,16 @@
       <c r="E325" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G325">
+        <f t="shared" si="10"/>
+        <v>595726.7274168001</v>
+      </c>
+      <c r="H325">
+        <f t="shared" si="11"/>
+        <v>2.4774182964111651</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
         <v>10</v>
       </c>
@@ -6466,8 +9058,16 @@
       <c r="E326" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G326">
+        <f t="shared" si="10"/>
+        <v>597802.73038319999</v>
+      </c>
+      <c r="H326">
+        <f t="shared" si="11"/>
+        <v>2.3382142069118297</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
         <v>10</v>
       </c>
@@ -6483,8 +9083,16 @@
       <c r="E327" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G327">
+        <f t="shared" si="10"/>
+        <v>599878.73334959999</v>
+      </c>
+      <c r="H327">
+        <f t="shared" si="11"/>
+        <v>2.1872131590607</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
         <v>10</v>
       </c>
@@ -6500,8 +9108,16 @@
       <c r="E328" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G328">
+        <f t="shared" si="10"/>
+        <v>601435.73557440005</v>
+      </c>
+      <c r="H328">
+        <f t="shared" si="11"/>
+        <v>2.0629518830305713</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
         <v>10</v>
       </c>
@@ -6517,8 +9133,16 @@
       <c r="E329" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G329">
+        <f t="shared" si="10"/>
+        <v>604030.7392824</v>
+      </c>
+      <c r="H329">
+        <f t="shared" si="11"/>
+        <v>1.8899298493575543</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
         <v>10</v>
       </c>
@@ -6534,8 +9158,16 @@
       <c r="E330" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G330">
+        <f t="shared" si="10"/>
+        <v>606106.74233639997</v>
+      </c>
+      <c r="H330">
+        <f t="shared" si="11"/>
+        <v>1.7542648471422244</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
         <v>10</v>
       </c>
@@ -6551,8 +9183,16 @@
       <c r="E331" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G331">
+        <f t="shared" si="10"/>
+        <v>608182.74530279997</v>
+      </c>
+      <c r="H331">
+        <f t="shared" si="11"/>
+        <v>1.6162404541426671</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
         <v>10</v>
       </c>
@@ -6568,8 +9208,16 @@
       <c r="E332" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G332">
+        <f t="shared" si="10"/>
+        <v>610258.74826919998</v>
+      </c>
+      <c r="H332">
+        <f t="shared" si="11"/>
+        <v>1.4864739299955694</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
         <v>10</v>
       </c>
@@ -6585,8 +9233,16 @@
       <c r="E333" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G333">
+        <f t="shared" si="10"/>
+        <v>612334.75123559998</v>
+      </c>
+      <c r="H333">
+        <f t="shared" si="11"/>
+        <v>1.3681673061586175</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
         <v>10</v>
       </c>
@@ -6602,8 +9258,16 @@
       <c r="E334" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G334">
+        <f t="shared" si="10"/>
+        <v>614410.75420199998</v>
+      </c>
+      <c r="H334">
+        <f t="shared" si="11"/>
+        <v>1.2623317523260966</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
         <v>10</v>
       </c>
@@ -6619,8 +9283,16 @@
       <c r="E335" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G335">
+        <f t="shared" si="10"/>
+        <v>617005.7579975999</v>
+      </c>
+      <c r="H335">
+        <f t="shared" si="11"/>
+        <v>1.1490809680992469</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
         <v>10</v>
       </c>
@@ -6636,8 +9308,16 @@
       <c r="E336" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G336">
+        <f t="shared" si="10"/>
+        <v>620119.76244720002</v>
+      </c>
+      <c r="H336">
+        <f t="shared" si="11"/>
+        <v>1.0358301838723969</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
         <v>10</v>
       </c>
@@ -6653,8 +9333,16 @@
       <c r="E337" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G337">
+        <f t="shared" si="10"/>
+        <v>623752.76763840008</v>
+      </c>
+      <c r="H337">
+        <f t="shared" si="11"/>
+        <v>0.92729818121400098</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
         <v>10</v>
       </c>
@@ -6670,8 +9358,16 @@
       <c r="E338" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G338">
+        <f t="shared" si="10"/>
+        <v>628423.7744004</v>
+      </c>
+      <c r="H338">
+        <f t="shared" si="11"/>
+        <v>0.82254120513956575</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
         <v>10</v>
       </c>
@@ -6687,8 +9383,16 @@
       <c r="E339" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G339">
+        <f t="shared" si="10"/>
+        <v>635689.78478280001</v>
+      </c>
+      <c r="H339">
+        <f t="shared" si="11"/>
+        <v>0.71547726849800619</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
         <v>10</v>
       </c>
@@ -6704,8 +9408,16 @@
       <c r="E340" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G340">
+        <f t="shared" si="10"/>
+        <v>646069.79970239999</v>
+      </c>
+      <c r="H340">
+        <f t="shared" si="11"/>
+        <v>0.62358016836508645</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
         <v>10</v>
       </c>
@@ -6721,8 +9433,16 @@
       <c r="E341" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G341">
+        <f t="shared" si="10"/>
+        <v>657487.81619280006</v>
+      </c>
+      <c r="H341">
+        <f t="shared" si="11"/>
+        <v>0.56738375498449267</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
         <v>10</v>
       </c>
@@ -6738,8 +9458,16 @@
       <c r="E342" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G342">
+        <f t="shared" si="10"/>
+        <v>668905.83259559993</v>
+      </c>
+      <c r="H342">
+        <f t="shared" si="11"/>
+        <v>0.535210237040319</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
         <v>10</v>
       </c>
@@ -6755,8 +9483,16 @@
       <c r="E343" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G343">
+        <f t="shared" si="10"/>
+        <v>680323.84899839992</v>
+      </c>
+      <c r="H343">
+        <f t="shared" si="11"/>
+        <v>0.51504816570669032</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
         <v>10</v>
       </c>
@@ -6772,8 +9508,16 @@
       <c r="E344" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G344">
+        <f t="shared" si="10"/>
+        <v>691741.86540120002</v>
+      </c>
+      <c r="H344">
+        <f t="shared" si="11"/>
+        <v>0.5026077381479841</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
         <v>10</v>
       </c>
@@ -6789,8 +9533,16 @@
       <c r="E345" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G345">
+        <f t="shared" si="10"/>
+        <v>703159.881804</v>
+      </c>
+      <c r="H345">
+        <f t="shared" si="11"/>
+        <v>0.49600144217988484</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
         <v>10</v>
       </c>
@@ -6806,8 +9558,16 @@
       <c r="E346" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G346">
+        <f t="shared" si="10"/>
+        <v>714577.89820679999</v>
+      </c>
+      <c r="H346">
+        <f t="shared" si="11"/>
+        <v>0.48973833185644655</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
         <v>10</v>
       </c>
@@ -6823,8 +9583,16 @@
       <c r="E347" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G347">
+        <f t="shared" si="10"/>
+        <v>720805.907106</v>
+      </c>
+      <c r="H347">
+        <f t="shared" si="11"/>
+        <v>0.48845139122729292</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
         <v>10</v>
       </c>
@@ -6840,8 +9608,16 @@
       <c r="E348" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G348">
+        <f t="shared" si="10"/>
+        <v>873679.47021840001</v>
+      </c>
+      <c r="H348">
+        <f t="shared" si="11"/>
+        <v>0.4747135888347363</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
         <v>10</v>
       </c>
@@ -6857,8 +9633,16 @@
       <c r="E349" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G349">
+        <f t="shared" si="10"/>
+        <v>779698.01327519992</v>
+      </c>
+      <c r="H349">
+        <f t="shared" si="11"/>
+        <v>0.4747135888347363</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
         <v>10</v>
       </c>
@@ -6874,8 +9658,16 @@
       <c r="E350" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G350">
+        <f t="shared" si="10"/>
+        <v>183121.13442839999</v>
+      </c>
+      <c r="H350">
+        <f t="shared" si="11"/>
+        <v>2.9233432609658836</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
         <v>10</v>
       </c>
@@ -6891,8 +9683,16 @@
       <c r="E351" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G351">
+        <f t="shared" si="10"/>
+        <v>193760.64971880004</v>
+      </c>
+      <c r="H351">
+        <f t="shared" si="11"/>
+        <v>2.9433980859548075</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
         <v>10</v>
       </c>
@@ -6908,8 +9708,16 @@
       <c r="E352" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G352">
+        <f t="shared" si="10"/>
+        <v>205438.16649240002</v>
+      </c>
+      <c r="H352">
+        <f t="shared" si="11"/>
+        <v>2.9672279397430219</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
         <v>10</v>
       </c>
@@ -6925,8 +9733,16 @@
       <c r="E353" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G353">
+        <f t="shared" si="10"/>
+        <v>217375.18363680001</v>
+      </c>
+      <c r="H353">
+        <f t="shared" si="11"/>
+        <v>2.9932670403190076</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
         <v>10</v>
       </c>
@@ -6942,8 +9758,16 @@
       <c r="E354" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G354">
+        <f t="shared" si="10"/>
+        <v>228051.77045880002</v>
+      </c>
+      <c r="H354">
+        <f t="shared" si="11"/>
+        <v>3.0143483562250775</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
         <v>10</v>
       </c>
@@ -6959,8 +9783,16 @@
       <c r="E355" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G355">
+        <f t="shared" si="10"/>
+        <v>240730.21718400001</v>
+      </c>
+      <c r="H355">
+        <f t="shared" si="11"/>
+        <v>3.043200341160833</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
         <v>10</v>
       </c>
@@ -6976,8 +9808,16 @@
       <c r="E356" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G356">
+        <f t="shared" si="10"/>
+        <v>252667.23432839997</v>
+      </c>
+      <c r="H356">
+        <f t="shared" si="11"/>
+        <v>3.070674142667257</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
         <v>10</v>
       </c>
@@ -6993,8 +9833,16 @@
       <c r="E357" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G357">
+        <f t="shared" si="10"/>
+        <v>264604.25156040001</v>
+      </c>
+      <c r="H357">
+        <f t="shared" si="11"/>
+        <v>3.0969944638901192</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
         <v>10</v>
       </c>
@@ -7010,8 +9858,16 @@
       <c r="E358" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G358">
+        <f t="shared" si="10"/>
+        <v>276541.26870479999</v>
+      </c>
+      <c r="H358">
+        <f t="shared" si="11"/>
+        <v>3.1272995347806822</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
         <v>10</v>
       </c>
@@ -7027,8 +9883,16 @@
       <c r="E359" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G359">
+        <f t="shared" si="10"/>
+        <v>289227.95359679998</v>
+      </c>
+      <c r="H359">
+        <f t="shared" si="11"/>
+        <v>3.1577094683207796</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
         <v>10</v>
       </c>
@@ -7044,8 +9908,16 @@
       <c r="E360" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G360">
+        <f t="shared" si="10"/>
+        <v>301141.90399680001</v>
+      </c>
+      <c r="H360">
+        <f t="shared" si="11"/>
+        <v>3.1875950908285335</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
         <v>10</v>
       </c>
@@ -7061,8 +9933,16 @@
       <c r="E361" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G361">
+        <f t="shared" si="10"/>
+        <v>312482.07036719995</v>
+      </c>
+      <c r="H361">
+        <f t="shared" si="11"/>
+        <v>3.2176773305272484</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
         <v>10</v>
       </c>
@@ -7078,8 +9958,16 @@
       <c r="E362" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G362">
+        <f t="shared" si="10"/>
+        <v>324289.3372824</v>
+      </c>
+      <c r="H362">
+        <f t="shared" si="11"/>
+        <v>3.2476523260965888</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
         <v>10</v>
       </c>
@@ -7095,8 +9983,16 @@
       <c r="E363" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G363">
+        <f t="shared" si="10"/>
+        <v>335707.35368519998</v>
+      </c>
+      <c r="H363">
+        <f t="shared" si="11"/>
+        <v>3.2806838037217543</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
         <v>10</v>
       </c>
@@ -7112,8 +10008,16 @@
       <c r="E364" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G364">
+        <f t="shared" ref="G364:G427" si="12">C364*24*365</f>
+        <v>348394.03857719997</v>
+      </c>
+      <c r="H364">
+        <f t="shared" ref="H364:H427" si="13">D364/4514*1000/1000*10000</f>
+        <v>3.3165751506424459</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
         <v>10</v>
       </c>
@@ -7129,8 +10033,16 @@
       <c r="E365" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G365">
+        <f t="shared" si="12"/>
+        <v>360411.78919560002</v>
+      </c>
+      <c r="H365">
+        <f t="shared" si="13"/>
+        <v>3.3518087284005316</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A366" t="s">
         <v>10</v>
       </c>
@@ -7146,8 +10058,16 @@
       <c r="E366" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G366">
+        <f t="shared" si="12"/>
+        <v>372037.40594759997</v>
+      </c>
+      <c r="H366">
+        <f t="shared" si="13"/>
+        <v>3.3857839654408508</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
         <v>10</v>
       </c>
@@ -7163,8 +10083,16 @@
       <c r="E367" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G367">
+        <f t="shared" si="12"/>
+        <v>384262.75682760001</v>
+      </c>
+      <c r="H367">
+        <f t="shared" si="13"/>
+        <v>3.4287773172352685</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A368" t="s">
         <v>10</v>
       </c>
@@ -7180,8 +10108,16 @@
       <c r="E368" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G368">
+        <f t="shared" si="12"/>
+        <v>394873.43875320005</v>
+      </c>
+      <c r="H368">
+        <f t="shared" si="13"/>
+        <v>3.4608555073105891</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
         <v>10</v>
       </c>
@@ -7197,8 +10133,16 @@
       <c r="E369" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G369">
+        <f t="shared" si="12"/>
+        <v>406291.45515600004</v>
+      </c>
+      <c r="H369">
+        <f t="shared" si="13"/>
+        <v>3.4981767877713779</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
         <v>10</v>
       </c>
@@ -7214,8 +10158,16 @@
       <c r="E370" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G370">
+        <f t="shared" si="12"/>
+        <v>418747.47304200003</v>
+      </c>
+      <c r="H370">
+        <f t="shared" si="13"/>
+        <v>3.5419327735932651</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
         <v>10</v>
       </c>
@@ -7231,8 +10183,16 @@
       <c r="E371" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G371">
+        <f t="shared" si="12"/>
+        <v>429819.48897960002</v>
+      </c>
+      <c r="H371">
+        <f t="shared" si="13"/>
+        <v>3.5813512915374388</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
         <v>10</v>
       </c>
@@ -7248,8 +10208,16 @@
       <c r="E372" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G372">
+        <f t="shared" si="12"/>
+        <v>442506.17387160001</v>
+      </c>
+      <c r="H372">
+        <f t="shared" si="13"/>
+        <v>3.6269661918475857</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
         <v>10</v>
       </c>
@@ -7265,8 +10233,16 @@
       <c r="E373" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G373">
+        <f t="shared" si="12"/>
+        <v>455077.52521679999</v>
+      </c>
+      <c r="H373">
+        <f t="shared" si="13"/>
+        <v>3.6765789477182098</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
         <v>10</v>
       </c>
@@ -7282,8 +10258,16 @@
       <c r="E374" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G374">
+        <f t="shared" si="12"/>
+        <v>466034.20769520005</v>
+      </c>
+      <c r="H374">
+        <f t="shared" si="13"/>
+        <v>3.7176716814355339</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
         <v>10</v>
       </c>
@@ -7299,8 +10283,16 @@
       <c r="E375" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G375">
+        <f t="shared" si="12"/>
+        <v>476298.88906799996</v>
+      </c>
+      <c r="H375">
+        <f t="shared" si="13"/>
+        <v>3.7611893420469649</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
         <v>10</v>
       </c>
@@ -7316,8 +10308,16 @@
       <c r="E376" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G376">
+        <f t="shared" si="12"/>
+        <v>490369.57599600003</v>
+      </c>
+      <c r="H376">
+        <f t="shared" si="13"/>
+        <v>3.8199119716437751</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
         <v>10</v>
       </c>
@@ -7333,8 +10333,16 @@
       <c r="E377" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G377">
+        <f t="shared" si="12"/>
+        <v>503448.39475440001</v>
+      </c>
+      <c r="H377">
+        <f t="shared" si="13"/>
+        <v>3.8708748249889235</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
         <v>12</v>
       </c>
@@ -7350,8 +10358,16 @@
       <c r="E378" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G378">
+        <f t="shared" si="12"/>
+        <v>181429.32123479998</v>
+      </c>
+      <c r="H378">
+        <f>D378/4514*1000/1000</f>
+        <v>0.37253599091714668</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
         <v>12</v>
       </c>
@@ -7367,8 +10383,16 @@
       <c r="E379" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G379">
+        <f t="shared" si="12"/>
+        <v>191887.3616496</v>
+      </c>
+      <c r="H379">
+        <f t="shared" ref="H379:H442" si="14">D379/4514*1000/1000</f>
+        <v>0.37508070181657066</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
         <v>12</v>
       </c>
@@ -7384,8 +10408,16 @@
       <c r="E380" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G380">
+        <f t="shared" si="12"/>
+        <v>204595.86638760002</v>
+      </c>
+      <c r="H380">
+        <f t="shared" si="14"/>
+        <v>0.37812560943730616</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
         <v>12</v>
       </c>
@@ -7401,8 +10433,16 @@
       <c r="E381" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G381">
+        <f t="shared" si="12"/>
+        <v>216245.32908600001</v>
+      </c>
+      <c r="H381">
+        <f t="shared" si="14"/>
+        <v>0.38122881922906515</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A382" t="s">
         <v>12</v>
       </c>
@@ -7418,8 +10458,16 @@
       <c r="E382" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G382">
+        <f t="shared" si="12"/>
+        <v>227894.79178439997</v>
+      </c>
+      <c r="H382">
+        <f t="shared" si="14"/>
+        <v>0.38433202879929113</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
         <v>12</v>
       </c>
@@ -7435,8 +10483,16 @@
       <c r="E383" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G383">
+        <f t="shared" si="12"/>
+        <v>239756.06287319996</v>
+      </c>
+      <c r="H383">
+        <f t="shared" si="14"/>
+        <v>0.3876406524147098</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A384" t="s">
         <v>12</v>
       </c>
@@ -7452,8 +10508,16 @@
       <c r="E384" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G384">
+        <f t="shared" si="12"/>
+        <v>251193.71718119999</v>
+      </c>
+      <c r="H384">
+        <f t="shared" si="14"/>
+        <v>0.39086405981391231</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
         <v>12</v>
       </c>
@@ -7469,8 +10533,16 @@
       <c r="E385" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G385">
+        <f t="shared" si="12"/>
+        <v>262843.17979200004</v>
+      </c>
+      <c r="H385">
+        <f t="shared" si="14"/>
+        <v>0.39423861253876824</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
         <v>12</v>
       </c>
@@ -7486,8 +10558,16 @@
       <c r="E386" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G386">
+        <f t="shared" si="12"/>
+        <v>274810.3551636</v>
+      </c>
+      <c r="H386">
+        <f t="shared" si="14"/>
+        <v>0.39777476074435092</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
         <v>12</v>
       </c>
@@ -7503,8 +10583,16 @@
       <c r="E387" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G387">
+        <f t="shared" si="12"/>
+        <v>285877.34470079996</v>
+      </c>
+      <c r="H387">
+        <f t="shared" si="14"/>
+        <v>0.40123971821001325</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
         <v>12</v>
       </c>
@@ -7520,8 +10608,16 @@
       <c r="E388" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G388">
+        <f t="shared" si="12"/>
+        <v>298215.1847556</v>
+      </c>
+      <c r="H388">
+        <f t="shared" si="14"/>
+        <v>0.4050281606114311</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
         <v>12</v>
       </c>
@@ -7537,8 +10633,16 @@
       <c r="E389" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G389">
+        <f t="shared" si="12"/>
+        <v>309441.03058560006</v>
+      </c>
+      <c r="H389">
+        <f t="shared" si="14"/>
+        <v>0.40860512029242357</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
         <v>12</v>
       </c>
@@ -7554,8 +10658,16 @@
       <c r="E390" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G390">
+        <f t="shared" si="12"/>
+        <v>321196.39747919998</v>
+      </c>
+      <c r="H390">
+        <f t="shared" si="14"/>
+        <v>0.41258165086397874</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
         <v>12</v>
       </c>
@@ -7571,8 +10683,16 @@
       <c r="E391" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G391">
+        <f t="shared" si="12"/>
+        <v>333622.49102999998</v>
+      </c>
+      <c r="H391">
+        <f t="shared" si="14"/>
+        <v>0.41705128001772263</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
         <v>12</v>
       </c>
@@ -7588,8 +10708,16 @@
       <c r="E392" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G392">
+        <f t="shared" si="12"/>
+        <v>343859.89761719998</v>
+      </c>
+      <c r="H392">
+        <f t="shared" si="14"/>
+        <v>0.42037513314133806</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
         <v>12</v>
       </c>
@@ -7605,8 +10733,16 @@
       <c r="E393" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G393">
+        <f t="shared" si="12"/>
+        <v>356038.8812916</v>
+      </c>
+      <c r="H393">
+        <f t="shared" si="14"/>
+        <v>0.42487102879929106</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
         <v>12</v>
       </c>
@@ -7622,8 +10758,16 @@
       <c r="E394" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G394">
+        <f t="shared" si="12"/>
+        <v>368747.38611719996</v>
+      </c>
+      <c r="H394">
+        <f t="shared" si="14"/>
+        <v>0.42976106823216659</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
         <v>12</v>
       </c>
@@ -7639,8 +10783,16 @@
       <c r="E395" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G395">
+        <f t="shared" si="12"/>
+        <v>380396.84872799995</v>
+      </c>
+      <c r="H395">
+        <f t="shared" si="14"/>
+        <v>0.43422099246787771</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
         <v>12</v>
       </c>
@@ -7656,8 +10808,16 @@
       <c r="E396" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G396">
+        <f t="shared" si="12"/>
+        <v>393528.97033440002</v>
+      </c>
+      <c r="H396">
+        <f t="shared" si="14"/>
+        <v>0.43964667766947274</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
         <v>12</v>
       </c>
@@ -7673,8 +10833,16 @@
       <c r="E397" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G397">
+        <f t="shared" si="12"/>
+        <v>404754.81616440002</v>
+      </c>
+      <c r="H397">
+        <f t="shared" si="14"/>
+        <v>0.44416791094373065</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A398" t="s">
         <v>12</v>
       </c>
@@ -7690,8 +10858,16 @@
       <c r="E398" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G398">
+        <f t="shared" si="12"/>
+        <v>416404.27886279998</v>
+      </c>
+      <c r="H398">
+        <f t="shared" si="14"/>
+        <v>0.44927905826318121</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A399" t="s">
         <v>12</v>
       </c>
@@ -7707,8 +10883,16 @@
       <c r="E399" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G399">
+        <f t="shared" si="12"/>
+        <v>428371.45423440001</v>
+      </c>
+      <c r="H399">
+        <f t="shared" si="14"/>
+        <v>0.45461692357111211</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A400" t="s">
         <v>12</v>
       </c>
@@ -7724,8 +10908,16 @@
       <c r="E400" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G400">
+        <f t="shared" si="12"/>
+        <v>439703.20425959997</v>
+      </c>
+      <c r="H400">
+        <f t="shared" si="14"/>
+        <v>0.45982696455471866</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
         <v>12</v>
       </c>
@@ -7741,8 +10933,16 @@
       <c r="E401" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G401">
+        <f t="shared" si="12"/>
+        <v>451352.66695800005</v>
+      </c>
+      <c r="H401">
+        <f t="shared" si="14"/>
+        <v>0.46531799202481172</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A402" t="s">
         <v>12</v>
       </c>
@@ -7758,8 +10958,16 @@
       <c r="E402" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G402">
+        <f t="shared" si="12"/>
+        <v>463002.12965640001</v>
+      </c>
+      <c r="H402">
+        <f t="shared" si="14"/>
+        <v>0.4710260937084626</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
         <v>12</v>
       </c>
@@ -7775,8 +10983,16 @@
       <c r="E403" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G403">
+        <f t="shared" si="12"/>
+        <v>473857.3108032</v>
+      </c>
+      <c r="H403">
+        <f t="shared" si="14"/>
+        <v>0.47626237062472304</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
         <v>12</v>
       </c>
@@ -7792,8 +11008,16 @@
       <c r="E404" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G404">
+        <f t="shared" si="12"/>
+        <v>486698.19578519999</v>
+      </c>
+      <c r="H404">
+        <f t="shared" si="14"/>
+        <v>0.4827053440407621</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
         <v>12</v>
       </c>
@@ -7809,8 +11033,16 @@
       <c r="E405" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G405">
+        <f t="shared" si="12"/>
+        <v>495302.91252119996</v>
+      </c>
+      <c r="H405">
+        <f t="shared" si="14"/>
+        <v>0.48707511120957026</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
         <v>12</v>
       </c>
@@ -7826,8 +11058,16 @@
       <c r="E406" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G406">
+        <f t="shared" si="12"/>
+        <v>507481.89628320001</v>
+      </c>
+      <c r="H406">
+        <f t="shared" si="14"/>
+        <v>0.49299827049180328</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
         <v>12</v>
       </c>
@@ -7843,8 +11083,16 @@
       <c r="E407" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G407">
+        <f t="shared" si="12"/>
+        <v>528662.73751320003</v>
+      </c>
+      <c r="H407">
+        <f t="shared" si="14"/>
+        <v>0.50175252658396108</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
         <v>12</v>
       </c>
@@ -7860,8 +11108,16 @@
       <c r="E408" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G408">
+        <f t="shared" si="12"/>
+        <v>545077.88952119998</v>
+      </c>
+      <c r="H408">
+        <f t="shared" si="14"/>
+        <v>0.50479417080194955</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
         <v>12</v>
       </c>
@@ -7877,8 +11133,16 @@
       <c r="E409" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G409">
+        <f t="shared" si="12"/>
+        <v>563258.11153680005</v>
+      </c>
+      <c r="H409">
+        <f t="shared" si="14"/>
+        <v>0.49822475897208685</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A410" t="s">
         <v>12</v>
       </c>
@@ -7894,8 +11158,16 @@
       <c r="E410" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G410">
+        <f t="shared" si="12"/>
+        <v>572612.98307640001</v>
+      </c>
+      <c r="H410">
+        <f t="shared" si="14"/>
+        <v>0.48782533761630481</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
         <v>12</v>
       </c>
@@ -7911,8 +11183,16 @@
       <c r="E411" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G411">
+        <f t="shared" si="12"/>
+        <v>579496.75655279995</v>
+      </c>
+      <c r="H411">
+        <f t="shared" si="14"/>
+        <v>0.47505414288879044</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A412" t="s">
         <v>12</v>
       </c>
@@ -7928,8 +11208,16 @@
       <c r="E412" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G412">
+        <f t="shared" si="12"/>
+        <v>585321.48790199996</v>
+      </c>
+      <c r="H412">
+        <f t="shared" si="14"/>
+        <v>0.45912312295081964</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
         <v>12</v>
       </c>
@@ -7945,8 +11233,16 @@
       <c r="E413" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G413">
+        <f t="shared" si="12"/>
+        <v>589557.65614799992</v>
+      </c>
+      <c r="H413">
+        <f t="shared" si="14"/>
+        <v>0.44418312804607885</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A414" t="s">
         <v>12</v>
       </c>
@@ -7962,8 +11258,16 @@
       <c r="E414" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G414">
+        <f t="shared" si="12"/>
+        <v>593264.30333039991</v>
+      </c>
+      <c r="H414">
+        <f t="shared" si="14"/>
+        <v>0.42760352525476297</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
         <v>12</v>
       </c>
@@ -7979,8 +11283,16 @@
       <c r="E415" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G415">
+        <f t="shared" si="12"/>
+        <v>597500.4715764001</v>
+      </c>
+      <c r="H415">
+        <f t="shared" si="14"/>
+        <v>0.40589804674346475</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A416" t="s">
         <v>12</v>
       </c>
@@ -7996,8 +11308,16 @@
       <c r="E416" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G416">
+        <f t="shared" si="12"/>
+        <v>599618.55574320001</v>
+      </c>
+      <c r="H416">
+        <f t="shared" si="14"/>
+        <v>0.39355292157731503</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
         <v>12</v>
       </c>
@@ -8013,8 +11333,16 @@
       <c r="E417" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G417">
+        <f t="shared" si="12"/>
+        <v>602266.16088600003</v>
+      </c>
+      <c r="H417">
+        <f t="shared" si="14"/>
+        <v>0.37623115906070004</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
         <v>12</v>
       </c>
@@ -8030,8 +11358,16 @@
       <c r="E418" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G418">
+        <f t="shared" si="12"/>
+        <v>603854.72398919996</v>
+      </c>
+      <c r="H418">
+        <f t="shared" si="14"/>
+        <v>0.36368906579530347</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
         <v>12</v>
       </c>
@@ -8047,8 +11383,16 @@
       <c r="E419" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G419">
+        <f t="shared" si="12"/>
+        <v>606502.32913199987</v>
+      </c>
+      <c r="H419">
+        <f t="shared" si="14"/>
+        <v>0.34457644018608774</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
         <v>12</v>
       </c>
@@ -8064,8 +11408,16 @@
       <c r="E420" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G420">
+        <f t="shared" si="12"/>
+        <v>608620.41321120004</v>
+      </c>
+      <c r="H420">
+        <f t="shared" si="14"/>
+        <v>0.32815212605228178</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
         <v>12</v>
       </c>
@@ -8081,8 +11433,16 @@
       <c r="E421" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G421">
+        <f t="shared" si="12"/>
+        <v>610738.49737799994</v>
+      </c>
+      <c r="H421">
+        <f t="shared" si="14"/>
+        <v>0.30874303987594148</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
         <v>12</v>
       </c>
@@ -8098,8 +11458,16 @@
       <c r="E422" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G422">
+        <f t="shared" si="12"/>
+        <v>612856.58145720011</v>
+      </c>
+      <c r="H422">
+        <f t="shared" si="14"/>
+        <v>0.29261720314576872</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
         <v>12</v>
       </c>
@@ -8115,8 +11483,16 @@
       <c r="E423" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G423">
+        <f t="shared" si="12"/>
+        <v>614974.66562400002</v>
+      </c>
+      <c r="H423">
+        <f t="shared" si="14"/>
+        <v>0.27052182210899423</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
         <v>12</v>
       </c>
@@ -8132,8 +11508,16 @@
       <c r="E424" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G424">
+        <f t="shared" si="12"/>
+        <v>617092.74970319995</v>
+      </c>
+      <c r="H424">
+        <f t="shared" si="14"/>
+        <v>0.25141121311475412</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
         <v>12</v>
       </c>
@@ -8149,8 +11533,16 @@
       <c r="E425" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G425">
+        <f t="shared" si="12"/>
+        <v>619210.83386999997</v>
+      </c>
+      <c r="H425">
+        <f t="shared" si="14"/>
+        <v>0.23379299025254766</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A426" t="s">
         <v>12</v>
       </c>
@@ -8166,8 +11558,16 @@
       <c r="E426" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G426">
+        <f t="shared" si="12"/>
+        <v>621328.91803679999</v>
+      </c>
+      <c r="H426">
+        <f t="shared" si="14"/>
+        <v>0.21587629020824101</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A427" t="s">
         <v>12</v>
       </c>
@@ -8183,8 +11583,16 @@
       <c r="E427" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G427">
+        <f t="shared" si="12"/>
+        <v>623447.00211600005</v>
+      </c>
+      <c r="H427">
+        <f t="shared" si="14"/>
+        <v>0.19706415848471423</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A428" t="s">
         <v>12</v>
       </c>
@@ -8200,8 +11608,16 @@
       <c r="E428" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G428">
+        <f t="shared" ref="G428:G491" si="15">C428*24*365</f>
+        <v>625565.08628279995</v>
+      </c>
+      <c r="H428">
+        <f t="shared" si="14"/>
+        <v>0.18272918504652191</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
         <v>12</v>
       </c>
@@ -8217,8 +11633,16 @@
       <c r="E429" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G429">
+        <f t="shared" si="15"/>
+        <v>627683.170362</v>
+      </c>
+      <c r="H429">
+        <f t="shared" si="14"/>
+        <v>0.16779725715551616</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A430" t="s">
         <v>12</v>
       </c>
@@ -8234,8 +11658,16 @@
       <c r="E430" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G430">
+        <f t="shared" si="15"/>
+        <v>629801.25452880003</v>
+      </c>
+      <c r="H430">
+        <f t="shared" si="14"/>
+        <v>0.15555162423571114</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
         <v>12</v>
       </c>
@@ -8251,8 +11683,16 @@
       <c r="E431" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G431">
+        <f t="shared" si="15"/>
+        <v>632448.85967160005</v>
+      </c>
+      <c r="H431">
+        <f t="shared" si="14"/>
+        <v>0.14151311127603011</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A432" t="s">
         <v>12</v>
       </c>
@@ -8268,8 +11708,16 @@
       <c r="E432" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G432">
+        <f t="shared" si="15"/>
+        <v>636155.50685400004</v>
+      </c>
+      <c r="H432">
+        <f t="shared" si="14"/>
+        <v>0.12597817875498449</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
         <v>12</v>
       </c>
@@ -8285,8 +11733,16 @@
       <c r="E433" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G433">
+        <f t="shared" si="15"/>
+        <v>640921.19616359996</v>
+      </c>
+      <c r="H433">
+        <f t="shared" si="14"/>
+        <v>0.11103616716880815</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A434" t="s">
         <v>12</v>
       </c>
@@ -8302,8 +11758,16 @@
       <c r="E434" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G434">
+        <f t="shared" si="15"/>
+        <v>647275.44848879997</v>
+      </c>
+      <c r="H434">
+        <f t="shared" si="14"/>
+        <v>9.6855618232166582E-2</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
         <v>12</v>
       </c>
@@ -8319,8 +11783,16 @@
       <c r="E435" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G435">
+        <f t="shared" si="15"/>
+        <v>656806.82710799994</v>
+      </c>
+      <c r="H435">
+        <f t="shared" si="14"/>
+        <v>8.4329789698715102E-2</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A436" t="s">
         <v>12</v>
       </c>
@@ -8336,8 +11808,16 @@
       <c r="E436" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G436">
+        <f t="shared" si="15"/>
+        <v>666338.20563959994</v>
+      </c>
+      <c r="H436">
+        <f t="shared" si="14"/>
+        <v>7.6196615507310592E-2</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
         <v>12</v>
       </c>
@@ -8353,8 +11833,16 @@
       <c r="E437" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G437">
+        <f t="shared" si="15"/>
+        <v>675340.06319519994</v>
+      </c>
+      <c r="H437">
+        <f t="shared" si="14"/>
+        <v>7.2103040784226843E-2</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A438" t="s">
         <v>12</v>
       </c>
@@ -8370,8 +11858,16 @@
       <c r="E438" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G438">
+        <f t="shared" si="15"/>
+        <v>733763.88367919996</v>
+      </c>
+      <c r="H438">
+        <f t="shared" si="14"/>
+        <v>6.2528241182986263E-2</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
         <v>12</v>
       </c>
@@ -8387,8 +11883,16 @@
       <c r="E439" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G439">
+        <f t="shared" si="15"/>
+        <v>743118.75521879992</v>
+      </c>
+      <c r="H439">
+        <f t="shared" si="14"/>
+        <v>6.2293627337173231E-2</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A440" t="s">
         <v>12</v>
       </c>
@@ -8404,8 +11908,16 @@
       <c r="E440" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G440">
+        <f t="shared" si="15"/>
+        <v>876028.53394800005</v>
+      </c>
+      <c r="H440">
+        <f t="shared" si="14"/>
+        <v>6.3578289410722202E-2</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
         <v>12</v>
       </c>
@@ -8421,8 +11933,16 @@
       <c r="E441" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G441">
+        <f t="shared" si="15"/>
+        <v>174016.21617360003</v>
+      </c>
+      <c r="H441">
+        <f t="shared" si="14"/>
+        <v>0.37100106225077539</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A442" t="s">
         <v>12</v>
       </c>
@@ -8438,8 +11958,16 @@
       <c r="E442" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G442">
+        <f t="shared" si="15"/>
+        <v>515248.20471960003</v>
+      </c>
+      <c r="H442">
+        <f t="shared" si="14"/>
+        <v>0.49376463092600797</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A443" t="s">
         <v>12</v>
       </c>
@@ -8455,8 +11983,16 @@
       <c r="E443" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G443">
+        <f t="shared" si="15"/>
+        <v>530074.79362440004</v>
+      </c>
+      <c r="H443">
+        <f t="shared" ref="H443:H506" si="16">D443/4514*1000/1000</f>
+        <v>0.49609598006202926</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A444" t="s">
         <v>12</v>
       </c>
@@ -8472,8 +12008,16 @@
       <c r="E444" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G444">
+        <f t="shared" si="15"/>
+        <v>541371.24225120002</v>
+      </c>
+      <c r="H444">
+        <f t="shared" si="16"/>
+        <v>0.49395457089056266</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A445" t="s">
         <v>12</v>
       </c>
@@ -8489,8 +12033,16 @@
       <c r="E445" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G445">
+        <f t="shared" si="15"/>
+        <v>553020.70494960004</v>
+      </c>
+      <c r="H445">
+        <f t="shared" si="16"/>
+        <v>0.48604125786442176</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A446" t="s">
         <v>12</v>
       </c>
@@ -8506,8 +12058,16 @@
       <c r="E446" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G446">
+        <f t="shared" si="15"/>
+        <v>562022.56250520004</v>
+      </c>
+      <c r="H446">
+        <f t="shared" si="16"/>
+        <v>0.47338952724856004</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A447" t="s">
         <v>12</v>
       </c>
@@ -8523,8 +12083,16 @@
       <c r="E447" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G447">
+        <f t="shared" si="15"/>
+        <v>567847.29385439993</v>
+      </c>
+      <c r="H447">
+        <f t="shared" si="16"/>
+        <v>0.46017465019937975</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A448" t="s">
         <v>12</v>
       </c>
@@ -8540,8 +12108,16 @@
       <c r="E448" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G448">
+        <f t="shared" si="15"/>
+        <v>572612.98307640001</v>
+      </c>
+      <c r="H448">
+        <f t="shared" si="16"/>
+        <v>0.44559081125387678</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
         <v>12</v>
       </c>
@@ -8557,8 +12133,16 @@
       <c r="E449" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G449">
+        <f t="shared" si="15"/>
+        <v>576319.63034639996</v>
+      </c>
+      <c r="H449">
+        <f t="shared" si="16"/>
+        <v>0.43204572684980058</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A450" t="s">
         <v>12</v>
       </c>
@@ -8574,8 +12158,16 @@
       <c r="E450" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G450">
+        <f t="shared" si="15"/>
+        <v>579496.75655279995</v>
+      </c>
+      <c r="H450">
+        <f t="shared" si="16"/>
+        <v>0.41810468941072221</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A451" t="s">
         <v>12</v>
       </c>
@@ -8591,8 +12183,16 @@
       <c r="E451" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G451">
+        <f t="shared" si="15"/>
+        <v>582144.36169559998</v>
+      </c>
+      <c r="H451">
+        <f t="shared" si="16"/>
+        <v>0.40555856269384138</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A452" t="s">
         <v>12</v>
       </c>
@@ -8608,8 +12208,16 @@
       <c r="E452" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G452">
+        <f t="shared" si="15"/>
+        <v>584791.9668384</v>
+      </c>
+      <c r="H452">
+        <f t="shared" si="16"/>
+        <v>0.39022664842711563</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A453" t="s">
         <v>12</v>
       </c>
@@ -8625,8 +12233,16 @@
       <c r="E453" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G453">
+        <f t="shared" si="15"/>
+        <v>587969.09304479999</v>
+      </c>
+      <c r="H453">
+        <f t="shared" si="16"/>
+        <v>0.37031606668143557</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A454" t="s">
         <v>12</v>
       </c>
@@ -8642,8 +12258,16 @@
       <c r="E454" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G454">
+        <f t="shared" si="15"/>
+        <v>590616.69818760001</v>
+      </c>
+      <c r="H454">
+        <f t="shared" si="16"/>
+        <v>0.35090496389011955</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A455" t="s">
         <v>12</v>
       </c>
@@ -8659,8 +12283,16 @@
       <c r="E455" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G455">
+        <f t="shared" si="15"/>
+        <v>592734.78226679994</v>
+      </c>
+      <c r="H455">
+        <f t="shared" si="16"/>
+        <v>0.33567455870624724</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A456" t="s">
         <v>12</v>
       </c>
@@ -8676,8 +12308,16 @@
       <c r="E456" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G456">
+        <f t="shared" si="15"/>
+        <v>594852.86643360008</v>
+      </c>
+      <c r="H456">
+        <f t="shared" si="16"/>
+        <v>0.31537004098360655</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A457" t="s">
         <v>12</v>
       </c>
@@ -8693,8 +12333,16 @@
       <c r="E457" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G457">
+        <f t="shared" si="15"/>
+        <v>596970.95060039998</v>
+      </c>
+      <c r="H457">
+        <f t="shared" si="16"/>
+        <v>0.29805029530350019</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A458" t="s">
         <v>12</v>
       </c>
@@ -8710,8 +12358,16 @@
       <c r="E458" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G458">
+        <f t="shared" si="15"/>
+        <v>599089.03467960004</v>
+      </c>
+      <c r="H458">
+        <f t="shared" si="16"/>
+        <v>0.27834273194505982</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A459" t="s">
         <v>12</v>
       </c>
@@ -8727,8 +12383,16 @@
       <c r="E459" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G459">
+        <f t="shared" si="15"/>
+        <v>600677.59778279997</v>
+      </c>
+      <c r="H459">
+        <f t="shared" si="16"/>
+        <v>0.26580063845813029</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A460" t="s">
         <v>12</v>
       </c>
@@ -8744,8 +12408,16 @@
       <c r="E460" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G460">
+        <f t="shared" si="15"/>
+        <v>602266.16088600003</v>
+      </c>
+      <c r="H460">
+        <f t="shared" si="16"/>
+        <v>0.24967681856446614</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A461" t="s">
         <v>12</v>
       </c>
@@ -8761,8 +12433,16 @@
       <c r="E461" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G461">
+        <f t="shared" si="15"/>
+        <v>604384.24496519996</v>
+      </c>
+      <c r="H461">
+        <f t="shared" si="16"/>
+        <v>0.23265555006645991</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A462" t="s">
         <v>12</v>
       </c>
@@ -8778,8 +12458,16 @@
       <c r="E462" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G462">
+        <f t="shared" si="15"/>
+        <v>606502.32913199987</v>
+      </c>
+      <c r="H462">
+        <f t="shared" si="16"/>
+        <v>0.21593275886132035</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A463" t="s">
         <v>12</v>
       </c>
@@ -8795,8 +12483,16 @@
       <c r="E463" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G463">
+        <f t="shared" si="15"/>
+        <v>608620.41321120004</v>
+      </c>
+      <c r="H463">
+        <f t="shared" si="16"/>
+        <v>0.19712062713779355</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A464" t="s">
         <v>12</v>
       </c>
@@ -8812,8 +12508,16 @@
       <c r="E464" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G464">
+        <f t="shared" si="15"/>
+        <v>610738.49737799994</v>
+      </c>
+      <c r="H464">
+        <f t="shared" si="16"/>
+        <v>0.18189022204253433</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A465" t="s">
         <v>12</v>
       </c>
@@ -8829,8 +12533,16 @@
       <c r="E465" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G465">
+        <f t="shared" si="15"/>
+        <v>612856.58145720011</v>
+      </c>
+      <c r="H465">
+        <f t="shared" si="16"/>
+        <v>0.16874915746566238</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A466" t="s">
         <v>12</v>
       </c>
@@ -8846,8 +12558,16 @@
       <c r="E466" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G466">
+        <f t="shared" si="15"/>
+        <v>615504.18668759987</v>
+      </c>
+      <c r="H466">
+        <f t="shared" si="16"/>
+        <v>0.15172587233052723</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A467" t="s">
         <v>12</v>
       </c>
@@ -8863,8 +12583,16 @@
       <c r="E467" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G467">
+        <f t="shared" si="15"/>
+        <v>618681.3128064</v>
+      </c>
+      <c r="H467">
+        <f t="shared" si="16"/>
+        <v>0.13539701727957465</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A468" t="s">
         <v>12</v>
       </c>
@@ -8880,8 +12608,16 @@
       <c r="E468" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G468">
+        <f t="shared" si="15"/>
+        <v>622387.96007640008</v>
+      </c>
+      <c r="H468">
+        <f t="shared" si="16"/>
+        <v>0.12080726260522817</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A469" t="s">
         <v>12</v>
       </c>
@@ -8897,8 +12633,16 @@
       <c r="E469" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G469">
+        <f t="shared" si="15"/>
+        <v>627153.64929840004</v>
+      </c>
+      <c r="H469">
+        <f t="shared" si="16"/>
+        <v>0.10655174864864865</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A470" t="s">
         <v>12</v>
       </c>
@@ -8914,8 +12658,16 @@
       <c r="E470" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G470">
+        <f t="shared" si="15"/>
+        <v>634037.4227748001</v>
+      </c>
+      <c r="H470">
+        <f t="shared" si="16"/>
+        <v>9.2332939299955688E-2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A471" t="s">
         <v>12</v>
       </c>
@@ -8931,8 +12683,16 @@
       <c r="E471" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G471">
+        <f t="shared" si="15"/>
+        <v>644098.32236999995</v>
+      </c>
+      <c r="H471">
+        <f t="shared" si="16"/>
+        <v>8.0199510345591501E-2</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A472" t="s">
         <v>12</v>
       </c>
@@ -8948,8 +12708,16 @@
       <c r="E472" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G472">
+        <f t="shared" si="15"/>
+        <v>654953.5035168</v>
+      </c>
+      <c r="H472">
+        <f t="shared" si="16"/>
+        <v>7.2703020336730165E-2</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A473" t="s">
         <v>12</v>
       </c>
@@ -8965,8 +12733,16 @@
       <c r="E473" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G473">
+        <f t="shared" si="15"/>
+        <v>666926.56236719992</v>
+      </c>
+      <c r="H473">
+        <f t="shared" si="16"/>
+        <v>6.815538825875056E-2</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A474" t="s">
         <v>12</v>
       </c>
@@ -8982,8 +12758,16 @@
       <c r="E474" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G474">
+        <f t="shared" si="15"/>
+        <v>677987.66833799996</v>
+      </c>
+      <c r="H474">
+        <f t="shared" si="16"/>
+        <v>6.5393801750110767E-2</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A475" t="s">
         <v>12</v>
       </c>
@@ -8999,8 +12783,16 @@
       <c r="E475" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G475">
+        <f t="shared" si="15"/>
+        <v>689637.1310364001</v>
+      </c>
+      <c r="H475">
+        <f t="shared" si="16"/>
+        <v>6.3691226739034115E-2</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A476" t="s">
         <v>12</v>
       </c>
@@ -9016,8 +12808,16 @@
       <c r="E476" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G476">
+        <f t="shared" si="15"/>
+        <v>703934.19887759991</v>
+      </c>
+      <c r="H476">
+        <f t="shared" si="16"/>
+        <v>6.2442865950376604E-2</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A477" t="s">
         <v>12</v>
       </c>
@@ -9033,8 +12833,16 @@
       <c r="E477" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G477">
+        <f t="shared" si="15"/>
+        <v>753179.65481400013</v>
+      </c>
+      <c r="H477">
+        <f t="shared" si="16"/>
+        <v>5.9867491559592381E-2</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A478" t="s">
         <v>12</v>
       </c>
@@ -9050,8 +12858,16 @@
       <c r="E478" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G478">
+        <f t="shared" si="15"/>
+        <v>851670.5665991999</v>
+      </c>
+      <c r="H478">
+        <f t="shared" si="16"/>
+        <v>5.949237831191849E-2</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A479" t="s">
         <v>12</v>
       </c>
@@ -9067,8 +12883,16 @@
       <c r="E479" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G479">
+        <f t="shared" si="15"/>
+        <v>863320.02929759992</v>
+      </c>
+      <c r="H479">
+        <f t="shared" si="16"/>
+        <v>5.9448010079751881E-2</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A480" t="s">
         <v>12</v>
       </c>
@@ -9084,8 +12908,16 @@
       <c r="E480" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G480">
+        <f t="shared" si="15"/>
+        <v>871262.8447260001</v>
+      </c>
+      <c r="H480">
+        <f t="shared" si="16"/>
+        <v>5.9417758994240136E-2</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A481" t="s">
         <v>12</v>
       </c>
@@ -9101,8 +12933,16 @@
       <c r="E481" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G481">
+        <f t="shared" si="15"/>
+        <v>181429.32123479998</v>
+      </c>
+      <c r="H481">
+        <f t="shared" si="16"/>
+        <v>0.37253599091714668</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A482" t="s">
         <v>12</v>
       </c>
@@ -9118,8 +12958,16 @@
       <c r="E482" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G482">
+        <f t="shared" si="15"/>
+        <v>191887.3616496</v>
+      </c>
+      <c r="H482">
+        <f t="shared" si="16"/>
+        <v>0.37508070181657066</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A483" t="s">
         <v>12</v>
       </c>
@@ -9135,8 +12983,16 @@
       <c r="E483" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G483">
+        <f t="shared" si="15"/>
+        <v>204595.86638760002</v>
+      </c>
+      <c r="H483">
+        <f t="shared" si="16"/>
+        <v>0.37812560943730616</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A484" t="s">
         <v>12</v>
       </c>
@@ -9152,8 +13008,16 @@
       <c r="E484" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G484">
+        <f t="shared" si="15"/>
+        <v>216245.32908600001</v>
+      </c>
+      <c r="H484">
+        <f t="shared" si="16"/>
+        <v>0.38122881922906515</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A485" t="s">
         <v>12</v>
       </c>
@@ -9169,8 +13033,16 @@
       <c r="E485" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G485">
+        <f t="shared" si="15"/>
+        <v>227894.79178439997</v>
+      </c>
+      <c r="H485">
+        <f t="shared" si="16"/>
+        <v>0.38433202879929113</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A486" t="s">
         <v>12</v>
       </c>
@@ -9186,8 +13058,16 @@
       <c r="E486" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G486">
+        <f t="shared" si="15"/>
+        <v>239756.06287319996</v>
+      </c>
+      <c r="H486">
+        <f t="shared" si="16"/>
+        <v>0.3876406524147098</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A487" t="s">
         <v>12</v>
       </c>
@@ -9203,8 +13083,16 @@
       <c r="E487" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G487">
+        <f t="shared" si="15"/>
+        <v>251193.71718119999</v>
+      </c>
+      <c r="H487">
+        <f t="shared" si="16"/>
+        <v>0.39086405981391231</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A488" t="s">
         <v>12</v>
       </c>
@@ -9220,8 +13108,16 @@
       <c r="E488" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G488">
+        <f t="shared" si="15"/>
+        <v>262843.17979200004</v>
+      </c>
+      <c r="H488">
+        <f t="shared" si="16"/>
+        <v>0.39423861253876824</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A489" t="s">
         <v>12</v>
       </c>
@@ -9237,8 +13133,16 @@
       <c r="E489" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G489">
+        <f t="shared" si="15"/>
+        <v>274810.3551636</v>
+      </c>
+      <c r="H489">
+        <f t="shared" si="16"/>
+        <v>0.39777476074435092</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A490" t="s">
         <v>12</v>
       </c>
@@ -9254,8 +13158,16 @@
       <c r="E490" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G490">
+        <f t="shared" si="15"/>
+        <v>285877.34470079996</v>
+      </c>
+      <c r="H490">
+        <f t="shared" si="16"/>
+        <v>0.40123971821001325</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A491" t="s">
         <v>12</v>
       </c>
@@ -9271,8 +13183,16 @@
       <c r="E491" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G491">
+        <f t="shared" si="15"/>
+        <v>298215.1847556</v>
+      </c>
+      <c r="H491">
+        <f t="shared" si="16"/>
+        <v>0.4050281606114311</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A492" t="s">
         <v>12</v>
       </c>
@@ -9288,8 +13208,16 @@
       <c r="E492" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G492">
+        <f t="shared" ref="G492:G509" si="17">C492*24*365</f>
+        <v>309441.03058560006</v>
+      </c>
+      <c r="H492">
+        <f t="shared" si="16"/>
+        <v>0.40860512029242357</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A493" t="s">
         <v>12</v>
       </c>
@@ -9305,8 +13233,16 @@
       <c r="E493" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G493">
+        <f t="shared" si="17"/>
+        <v>321196.39747919998</v>
+      </c>
+      <c r="H493">
+        <f t="shared" si="16"/>
+        <v>0.41258165086397874</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A494" t="s">
         <v>12</v>
       </c>
@@ -9322,8 +13258,16 @@
       <c r="E494" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G494">
+        <f t="shared" si="17"/>
+        <v>333622.49102999998</v>
+      </c>
+      <c r="H494">
+        <f t="shared" si="16"/>
+        <v>0.41705128001772263</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A495" t="s">
         <v>12</v>
       </c>
@@ -9339,8 +13283,16 @@
       <c r="E495" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G495">
+        <f t="shared" si="17"/>
+        <v>343859.89761719998</v>
+      </c>
+      <c r="H495">
+        <f t="shared" si="16"/>
+        <v>0.42037513314133806</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A496" t="s">
         <v>12</v>
       </c>
@@ -9356,8 +13308,16 @@
       <c r="E496" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G496">
+        <f t="shared" si="17"/>
+        <v>356038.8812916</v>
+      </c>
+      <c r="H496">
+        <f t="shared" si="16"/>
+        <v>0.42487102879929106</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A497" t="s">
         <v>12</v>
       </c>
@@ -9373,8 +13333,16 @@
       <c r="E497" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G497">
+        <f t="shared" si="17"/>
+        <v>368747.38611719996</v>
+      </c>
+      <c r="H497">
+        <f t="shared" si="16"/>
+        <v>0.42976106823216659</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A498" t="s">
         <v>12</v>
       </c>
@@ -9390,8 +13358,16 @@
       <c r="E498" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G498">
+        <f t="shared" si="17"/>
+        <v>380396.84872799995</v>
+      </c>
+      <c r="H498">
+        <f t="shared" si="16"/>
+        <v>0.43422099246787771</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A499" t="s">
         <v>12</v>
       </c>
@@ -9407,8 +13383,16 @@
       <c r="E499" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G499">
+        <f t="shared" si="17"/>
+        <v>393528.97033440002</v>
+      </c>
+      <c r="H499">
+        <f t="shared" si="16"/>
+        <v>0.43964667766947274</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A500" t="s">
         <v>12</v>
       </c>
@@ -9424,8 +13408,16 @@
       <c r="E500" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G500">
+        <f t="shared" si="17"/>
+        <v>404754.81616440002</v>
+      </c>
+      <c r="H500">
+        <f t="shared" si="16"/>
+        <v>0.44416791094373065</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A501" t="s">
         <v>12</v>
       </c>
@@ -9441,8 +13433,16 @@
       <c r="E501" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G501">
+        <f t="shared" si="17"/>
+        <v>416404.27886279998</v>
+      </c>
+      <c r="H501">
+        <f t="shared" si="16"/>
+        <v>0.44927905826318121</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A502" t="s">
         <v>12</v>
       </c>
@@ -9458,8 +13458,16 @@
       <c r="E502" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G502">
+        <f t="shared" si="17"/>
+        <v>428371.45423440001</v>
+      </c>
+      <c r="H502">
+        <f t="shared" si="16"/>
+        <v>0.45461692357111211</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A503" t="s">
         <v>12</v>
       </c>
@@ -9475,8 +13483,16 @@
       <c r="E503" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G503">
+        <f t="shared" si="17"/>
+        <v>439703.20425959997</v>
+      </c>
+      <c r="H503">
+        <f t="shared" si="16"/>
+        <v>0.45982696455471866</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A504" t="s">
         <v>12</v>
       </c>
@@ -9492,8 +13508,16 @@
       <c r="E504" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G504">
+        <f t="shared" si="17"/>
+        <v>451352.66695800005</v>
+      </c>
+      <c r="H504">
+        <f t="shared" si="16"/>
+        <v>0.46531799202481172</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A505" t="s">
         <v>12</v>
       </c>
@@ -9509,8 +13533,16 @@
       <c r="E505" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G505">
+        <f t="shared" si="17"/>
+        <v>463002.12965640001</v>
+      </c>
+      <c r="H505">
+        <f t="shared" si="16"/>
+        <v>0.4710260937084626</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A506" t="s">
         <v>12</v>
       </c>
@@ -9526,8 +13558,16 @@
       <c r="E506" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G506">
+        <f t="shared" si="17"/>
+        <v>473857.3108032</v>
+      </c>
+      <c r="H506">
+        <f t="shared" si="16"/>
+        <v>0.47626237062472304</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A507" t="s">
         <v>12</v>
       </c>
@@ -9543,8 +13583,16 @@
       <c r="E507" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G507">
+        <f t="shared" si="17"/>
+        <v>486698.19578519999</v>
+      </c>
+      <c r="H507">
+        <f t="shared" ref="H507:H509" si="18">D507/4514*1000/1000</f>
+        <v>0.4827053440407621</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A508" t="s">
         <v>12</v>
       </c>
@@ -9560,8 +13608,16 @@
       <c r="E508" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="G508">
+        <f t="shared" si="17"/>
+        <v>495302.91252119996</v>
+      </c>
+      <c r="H508">
+        <f t="shared" si="18"/>
+        <v>0.48707511120957026</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A509" t="s">
         <v>12</v>
       </c>
@@ -9576,6 +13632,14 @@
       </c>
       <c r="E509" t="s">
         <v>11</v>
+      </c>
+      <c r="G509">
+        <f t="shared" si="17"/>
+        <v>507481.89628320001</v>
+      </c>
+      <c r="H509">
+        <f t="shared" si="18"/>
+        <v>0.49299827049180328</v>
       </c>
     </row>
   </sheetData>

--- a/Geerts 2023 Figure 3.xlsx
+++ b/Geerts 2023 Figure 3.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elber\Documents\git\JSON2SBML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ADC0C43D-A9F3-4477-B507-3098A7F4F117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F693A6F8-CF50-4363-BF63-72F1E9D78341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{9ED6A267-9247-42AA-8654-D33B0E6EB95C}"/>
   </bookViews>
   <sheets>
     <sheet name="Geerts 2023 Figure 3" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -10013,7 +10026,7 @@
         <v>348394.03857719997</v>
       </c>
       <c r="H364">
-        <f t="shared" ref="H364:H427" si="13">D364/4514*1000/1000*10000</f>
+        <f t="shared" ref="H364:H377" si="13">D364/4514*1000/1000*10000</f>
         <v>3.3165751506424459</v>
       </c>
     </row>
